--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_03_Current_Electricity.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_03_Current_Electricity.xlsx
@@ -1168,11 +1168,6 @@
           <t>একটি ধাতব পরিবাহীতে মুক্ত ইলেকট্রন ঘনত্ব $n$ এবং ইলেকট্রনের আধান $e$। পরিবাহীর ভেতর সুষম তড়িৎক্ষেত্র $E$ প্রয়োগ করা হলে ইলেকট্রনগুলোর গড় শিথিলকরণ কাল (relaxation time) $\tau$ এবং ভর $m$ বিবেচনা করে তাড়ন বেগ $v_d$ এবং প্রবাহ ঘনত্ব $J$-এর আণুবীক্ষণিক সমীকরণ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>পরিবাহীতে তড়িৎক্ষেত্র $E$ প্রয়োগ করলে প্রতিটি ইলেকট্রন বল লাভ করে $F = e E$। ফলে ইলেকট্রনের ত্বরণ $a = \frac{e E}{m}$। দুটি ধারাবাহিক সংঘর্ষের মধ্যবর্তী গড় সময়কাল বা শিথিলকরণ কাল $\tau$ হলে অর্জিত নিট গড় তাড়ন বেগ $v_d = a \tau = \frac{e E \tau}{m}$। পরিবাহীর প্রস্থচ্ছেদের ক্ষেত্রফল $A$ হলে $\Delta t$ সময়ে অতিক্রান্ত মোট আধান $\Delta Q = n (A v_d \Delta t) e$। প্রবাহ $I = \frac{\Delta Q}{\Delta t} = n e A v_d$। অতএব প্রবাহ ঘনত্ব $J = \frac{I}{A} = n e v_d = \left(\frac{n e^2 \tau}{m}\right) E$।</t>
@@ -1218,11 +1213,6 @@
           <t>ড্রুডের চিরায়ত মুক্ত ইলেকট্রন তত্ত্বের সাহায্যে ওহমের সূত্রের আণুবীক্ষণিক রূপ $\vec{J} = \sigma \vec{E}$ প্রতিষ্ঠা করো এবং পরিবাহীর উপাদানের পরিবাহিতাঙ্ক $\sigma$ ও রোধাঙ্ক $\rho$-এর রাশিমালা ইলেকট্রনের আণুবীক্ষণিক রাশির ($n, e, m, \tau$) মাধ্যমে প্রকাশ করো।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>প্রবাহ ঘনত্ব $J = n e v_d$ এবং $v_d = \frac{e E \tau}{m}$ সমীকরণদ্বয় একত্রিত করলে পাই $J = \left(\frac{n e^2 \tau}{m}\right) E$। চিরায়ত ওহমের সূত্রানুযায়ী প্রবাহ ঘনত্ব তড়িৎক্ষেত্রের সমানুপাতিক, অর্থাৎ $\vec{J} = \sigma \vec{E}$। তুলনা করে পরিবাহিতাঙ্ক পাওয়া যায় $\sigma = \frac{n e^2 \tau}{m}$। রোধাঙ্ক পরিবাহিতাঙ্কের বিপরীত রাশি হওয়ায় $\rho = \frac{1}{\sigma} = \frac{m}{n e^2 \tau}$। এটি প্রমাণ করে যে রোধাঙ্ক মূলত পরিবাহীর মুক্ত ইলেকট্রন ঘনত্ব $n$ এবং সংঘর্ষের শিথিলকরণ কাল $\tau$-এর ওপর নির্ভরশীল।</t>
@@ -1268,11 +1258,6 @@
           <t>তাপমাত্রা বৃদ্ধির সাথে সাথে বিশুদ্ধ ধাতব পরিবাহীর রোধাঙ্ক বৃদ্ধি পায় কেন? আণুবীক্ষণিক রাশি শিথিলকরণ কাল $\tau$ এবং জালিকা কম্পন বা ফোনন বিচ্ছুরণের (phonon scattering) ভিত্তিতে এর বৈজ্ঞানিক ব্যাখ্যা দাও।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>ধাতব পরিবাহীতে মুক্ত ইলেকট্রন ঘনত্ব $n$ তাপমাত্রার সাথে প্রায় অপরিবর্তিত থাকে (যেহেতু ধাতুটিতে মুক্ত ইলেকট্রন ইতোমধ্যে আয়নিত অবস্থায় সম্পূর্ণ উন্মুক্ত থাকে)। কিন্তু তাপমাত্রা $T$ বৃদ্ধির সাথে সাথে ল্যাটিস আয়নগুলোর তাপীয় কম্পনের বিস্তার বৃদ্ধি পায়, যা কোয়ান্টাম দৃষ্টিকোণ থেকে ফোনন বিচ্ছুরণ বাড়ায়। ফলে ইলেকট্রনের তাপীয় বেগ $v_{\text{th}} \propto \sqrt{T}$ বাড়ে এবং সংঘর্ষের গড় মুক্ত পথ $\lambda$ কমে যায়। এতে গড় শিথিলকরণ কাল $\tau = \lambda / v_{\text{th}}$ উল্লেখযোগ্য হারে হ্রাস পায়। ফলে রোধাঙ্ক $\rho = \frac{m}{n e^2 \tau}$ তাপমাত্রা বৃদ্ধির সাথে সাথে রৈখিকভাবে বৃদ্ধি পায়।</t>
@@ -1318,11 +1303,6 @@
           <t>বিশুদ্ধ ধাতুর রোধের উষ্ণতা সহগ ($\alpha$) ধনাত্মক কিন্তু বিশুদ্ধ অর্ধপরিবাহীর উষ্ণতা সহগ ঋণাত্মক কেন? $\rho = \frac{m}{n e^2 \tau}$ সমীকরণের আলোকে গাণিতিক যুক্তিসহ ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>রোধাঙ্ক $\rho = \frac{m}{n e^2 \tau}$। ধাতুর ক্ষেত্রে $n$ স্থির থাকায় $\tau$ কমে যাওয়ার প্রভাব প্রধান হয়ে ওঠে এবং $\frac{d\rho}{dT} &gt; 0$ হওয়ায় $\alpha &gt; 0$ হয়। অপরপক্ষে, অভ্যন্তরীণ অর্ধপরিবাহীতে পরম শূন্য তাপমাত্রায় যোজ্যতা ব্যান্ড পূর্ণ ও পরিবহন ব্যান্ড শূন্য থাকে। তাপমাত্রা বৃদ্ধি পেলে তাপীয় শক্তিতে সমযোজী বন্ধন ভেঙে ইলেকট্রন-হোল জোড় সৃষ্টি হয়, যার ঘনত্ব $n(T) = n_0 e^{-E_g / (2 k_B T)}$ হারে সূচকীয়ভাবে বৃদ্ধি পায়। $n$-এর এই সূচকীয় বৃদ্ধি $\tau$-এর সামান্য হ্রাসকে সম্পূর্ণ নিষ্ক্রিয় করে দেয়। ফলে $\frac{d\rho}{dT} &lt; 0$ হয়, অর্থাৎ উষ্ণতা সহগ ঋণাত্মক ($\alpha &lt; 0$) হয়।</t>
@@ -1368,11 +1348,6 @@
           <t>ইলেকট্রন গতিশীলতা বা মোবিলিটি ($\mu$)-এর সংজ্ঞা দাও। পরিবাহিতাঙ্ক $\sigma$ এবং গতিশীলতা $\mu$-এর সম্পর্ক প্রতিষ্ঠা করো। এসআই এককে $\mu$-এর মাত্রা ও একক কী?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>প্রতি একক তড়িৎক্ষেত্রের জন্য পরিবাহীর মুক্ত আধান বাহকের অর্জিত তাড়ন বেগকে আধানের মোবিলিটি বা গতিশীলতা বলে: $\mu \equiv \frac{v_d}{E}$। ড্রুড মডেল থেকে $v_d = \frac{e E \tau}{m}$, সুতরাং $\mu = \frac{e \tau}{m}$। প্রবাহ ঘনত্ব $J = n e v_d = n e \mu E$। ওহমের সূত্র $J = \sigma E$-এর সাথে তুলনা করলে পাই $\sigma = n e \mu$। এককের ক্ষেত্রে: $\frac{\text{m/s}}{\text{V/m}} = \text{m}^2 \text{V}^{-1}\text{s}^{-1}$। মাত্রা সমীকরণ: $\frac{[L T^{-1}]}{[M L T^{-3} I^{-1}]} = [M^{-1} T^2 I]$।</t>
@@ -1418,11 +1393,6 @@
           <t>কক্ষ তাপমাত্রায় তামার তারে সাধারণ প্রবাহের জন্য ইলেকট্রনের গড় তাড়ন বেগ ($v_d$) প্রায় $10^{-4}\text{ m/s}$ হলেও সুইচ টেপার সাথে সাথে প্রায় আলোর গতিতে বাতি জ্বলে ওঠে কেন? তাড়ন বেগ ও তড়িৎ সংকেত সঞ্চালন বেগের পার্থক্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>কক্ষ তাপমাত্রায় ইলেকট্রনগুলোর বিশৃঙ্খল তাপীয় বেগ $v_{\text{th}} \approx 10^5 - 10^6\text{ m/s}$, কিন্তু তাদের গড় ভেক্টর বেগ শূন্য। বাহ্যিক তড়িৎক্ষেত্র $E$ প্রয়োগ করলে তাদের ওপর অতি ক্ষুদ্র তাড়ন বেগ $v_d \sim 10^{-4}\text{ m/s}$ বা কয়েক মিলিমিটার প্রতি সেকেন্ড আরোপিত হয়। তবে বর্তনী বন্ধ করার মুহূর্তে পরিবাহীর চারপাশের স্থানে পয়েন্টিং ভেক্টর দ্বারা বাহিত তড়িৎচৌম্বক তরঙ্গের সংকেত প্রায় আলোর গতিতে ($\sim 3 \times 10^8\text{ m/s}$) সমগ্র বর্তনীতে ছড়িয়ে পড়ে। এই ক্ষেত্র সমগ্র তারে ইতোমধ্যে উপস্থিত মুক্ত ইলেকট্রনগুলোকে একযোগে তাড়িত করে, ফলে দূরবর্তী বাল্বও তাৎক্ষণিকভাবে জ্বলে ওঠে।</t>
@@ -1468,11 +1438,6 @@
           <t>স্থির তড়িৎবিদ্যায় পরিবাহীর অভ্যন্তরে নিট তড়িৎক্ষেত্র শূন্য হয়, কিন্তু চল তড়িৎবিদ্যায় একটি তড়িৎবাহী তারের অভ্যন্তরে অশূন্য তড়িৎক্ষেত্র কীভাবে বিদ্যমান থাকে এবং এই ক্ষেত্র বজায় রাখতে তারের পৃষ্ঠ আধানের ভূমিকা কী?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>চল তড়িৎবিদ্যায় পরিবাহী স্থির সাম্যাবস্থায় থাকে না, বরং এটি একটি অ-সাম্যাবস্থাগত গতিশীল ব্যবস্থা। তারের অভ্যন্তরে ওহমের নিয়ম ($E = J/\sigma$) অনুসারে অবিরাম কারেন্ট প্রবাহ বজায় রাখতে একটি স্থির তড়িৎক্ষেত্র $E$ প্রয়োজন। গবেষণায় দেখা গেছে (যেমন Sommerfeld ও পরবর্তীতে Chabay &amp; Sherwood), ব্যাটারি ও বর্তনীর জ্যামিতির কারণে তারের বহিরাবরণী পৃষ্ঠে অতিসূক্ষ্ম পৃষ্ঠ আধান জমা হয়। এই পৃষ্ঠ আধানের ঘনত্ব তারের দৈর্ঘ্য বরাবর একটি গ্রেডিয়েন্ট তৈরি করে। এই পৃষ্ঠ আধানগুলোই যৌথভাবে তারের বাঁকানো পথের অভ্যন্তরে অক্ষীয় অভিমুখে তড়িৎক্ষেত্র সৃষ্টি ও পরিচালিত করে।</t>
@@ -1518,11 +1483,6 @@
           <t>একটি অসুষম প্রস্থচ্ছেদের ধাতব তারের মধ্য দিয়ে স্থির মানের তড়িৎ প্রবাহিত হচ্ছে। তারের যে অংশের ব্যাস $2\text{ mm}$ সেখান থেকে অন্য একটি অংশে যেখানে ব্যাস $1\text{ mm}$ হয়েছে, সেখানে প্রবাহ ঘনত্ব $J$, তাড়ন বেগ $v_d$ এবং অভ্যন্তরীণ তড়িৎক্ষেত্র $E$-এর অনুপাত কত হবে?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>স্থির প্রবাহ অবস্থায় আধান সংরক্ষণশীলতা অনুসারে তারের প্রতিটি প্রস্থচ্ছেদে মোট প্রবাহ $I$ ধ্রুবক: $I = J_1 A_1 = J_2 A_2$। প্রস্থচ্ছেদের ক্ষেত্রফল $A \propto d^2$। সুতরাং $A_1 / A_2 = (d_1 / d_2)^2 = (2 / 1)^2 = 4$। অতএব প্রবাহ ঘনত্ব $J_2 / J_1 = A_1 / A_2 = 4$। যেহেতু $J = n e v_d$ এবং উপাদান একই হওয়ায় $n$ ধ্রুবক, তাই $v_{d2} / v_{d1} = J_2 / J_1 = 4$। আবার ওহমের সূত্রানুযায়ী $E = J/\sigma$, পরিবাহিতাঙ্ক $\sigma$ ধ্রুবক হওয়ায় $E_2 / E_1 = J_2 / J_1 = 4$।</t>
@@ -1566,11 +1526,6 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>প্রস্থ $w$ এবং পুরুত্ব $t$ বিশিষ্ট একটি পরিবাহী পাতের মধ্য দিয়ে $I$ প্রবাহ চলছে এবং পাতের অভিলম্ব বরাবর একটি সুষম চৌম্বক ক্ষেত্র $B$ প্রয়োগ করা হলো। আবিষ্ট হল ভোল্টেজ $V_H$-এর রাশিমালা বের করো এবং দেখাও কীভাবে এর চিহ্ন থেকে আধান বাহকের প্রকৃতি (ইলেকট্রন নাকি হোল) নির্ণয় করা যায়।</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1668,11 +1623,6 @@
           <t>একটি সুষম ধাতব তারকে টেনে এর দৈর্ঘ্য $n$ গুণ বৃদ্ধি করা হলো ($L' = n L$)। উপাদানের ঘনত্ব ও রোধাঙ্ক অপরিবর্তিত থাকলে তারটির নতুন রোধ পূর্বের রোধের কত গুণ হবে? তারের দৈর্ঘ্য যদি অতিক্ষুদ্র ভগ্নাংশ $x\%$ ($x \ll 1$) প্রসারিত করা হয়, তবে রোধের শতকরা বৃদ্ধি কত হবে?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>টেনে লম্বা করার প্রক্রিয়ায় তারের মোট উপাদান বা আয়তন ধ্রুব থাকে: $V = A L = A' L' \implies A' = A \left(\frac{L}{L'}\right) = \frac{A}{n}$। মূল রোধ $R = \rho \frac{L}{A}$। নতুন রোধ $R' = \rho \frac{L'}{A'} = \rho \frac{n L}{A / n} = n^2 \left(\rho \frac{L}{A}\right) = n^2 R$। ক্ষুদ্র পরিবর্তনের ক্ষেত্রে ব্যবকলন পদ্ধতি প্রয়োগ করে: $R = \rho \frac{L}{A} = \rho \frac{L^2}{V} \implies \ln R = \ln(\rho / V) + 2 \ln L$। উভয়পাশে ব্যবকলন করলে: $\frac{dR}{R} = 2 \frac{dL}{L}$। শতকরা হিসাবে: $\frac{\Delta R}{R} \times 100\% = 2 \left(\frac{\Delta L}{L} \times 100\%\right) = 2x\%$।</t>
@@ -1718,11 +1668,6 @@
           <t>দৈর্ঘ্য $L$ এবং রোধাঙ্ক $\rho$ বিশিষ্ট একটি পরিবাহী খণ্ড একটি কর্তিত শঙ্কুর (truncated cone) ন্যায় তৈরি যার দুই প্রান্তের বৃত্তাকার ব্যাসার্ধ যথাক্রমে $a$ এবং $b$ ($b &gt; a$)। অক্ষ বরাবর তড়িৎ প্রবাহিত হলে পরিবাহী খণ্ডটির মোট রোধ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>শঙ্কুটির দৈর্ঘ্য বরাবর অক্ষকে $x$-অক্ষ ধরি, যেখানে $x=0$ বিন্দুতে ব্যাসার্ধ $a$ এবং $x=L$ বিন্দুতে ব্যাসার্ধ $b$। যেকোনো দূরত্ব $x$-এ বৃত্তাকার প্রস্থচ্ছেদের ব্যাসার্ধ রৈখিকভাবে বাড়ে: $r(x) = a + \left(\frac{b - a}{L}\right) x$। $dx$ পুরুত্বের একটি চাতকের প্রস্থচ্ছেদ ক্ষেত্রফল $A(x) = \pi [r(x)]^2$। এই ক্ষুদ্র অংশের রোধ $dR = \rho \frac{dx}{A(x)} = \frac{\rho dx}{\pi [a + \beta x]^2}$, যেখানে $\beta = \frac{b - a}{L}$। সম্পূর্ণ রোধ $R = \int_0^L dR = \frac{\rho}{\pi} \int_0^L \frac{dx}{(a + \beta x)^2} = \frac{\rho}{\pi \beta} \left[-\frac{1}{a + \beta x}\right]_0^L = \frac{\rho L}{\pi (b - a)} \left[\frac{1}{a} - \frac{1}{b}\right] = \frac{\rho L}{\pi (b - a)} \cdot \frac{b - a}{a b} = \frac{\rho L}{\pi a b}$।</t>
@@ -1768,11 +1713,6 @@
           <t>অভ্যন্তরীণ ব্যাসার্ধ $r_1$ এবং বহিঃস্থ ব্যাসার্ধ $r_2$ বিশিষ্ট একটি ফাঁপা পরিবাহী গোলকীয় খোলকের উপাদানের রোধাঙ্ক $\rho$। গোলকটির ভেতরের পৃষ্ঠ ও বাইরের পৃষ্ঠের মধ্যবর্তী ব্যাসার্ধীয় (radial) রোধের মান কত?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>কেন্দ্র থেকে $r$ ব্যাসার্ধে $dr$ বেধের একটি গোলকীয় খোলক বিবেচনা করি। এই খোলকের মধ্য দিয়ে ব্যাসার্ধীয় বহির্মুখী প্রবাহের জন্য পৃষ্ঠ ক্ষেত্রফল $A(r) = 4 \pi r^2$ এবং প্রবাহের পথ বরাবর দৈর্ঘ্য $dr$। ক্ষুদ্র স্তরের রোধ $dR = \rho \frac{dr}{4 \pi r^2}$। যেহেতু সমস্ত স্তরের মধ্য দিয়ে একই প্রবাহ ধারাবাহিকভাবে যায়, তাই তারা শ্রেণীতে যুক্ত। মোট রোধ: $R = \int_{r_1}^{r_2} dR = \frac{\rho}{4 \pi} \int_{r_1}^{r_2} \frac{dr}{r^2} = \frac{\rho}{4 \pi} \left[-\frac{1}{r}\right]_{r_1}^{r_2} = \frac{\rho}{4 \pi} \left(\frac{1}{r_1} - \frac{1}{r_2}\right) = \frac{\rho (r_2 - r_1)}{4 \pi r_1 r_2}$।</t>
@@ -1818,11 +1758,6 @@
           <t>দৈর্ঘ্য $L$, অভ্যন্তরীণ ব্যাসার্ধ $a$ এবং বহিঃস্থ ব্যাসার্ধ $b$ বিশিষ্ট একটি ফাঁপা সমাক্ষীয় চোঙের দুই স্তরের মধ্যবর্তী উপাদানটির রোধাঙ্ক $\rho$। অভ্যন্তরীণ বেলন থেকে বহিঃস্থ বেলনের দিকে ব্যাসার্ধীয়ভাবে তড়িৎ প্রবাহিত হলে মোট রোধ কত?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>অক্ষ থেকে $r$ ব্যাসার্ধে $dr$ বেধের একটি চোঙাকার খোলক বিবেচনা করি যার পৃষ্ঠ ক্ষেত্রফল $A(r) = 2 \pi r L$। ব্যাসার্ধীয় প্রবাহের অতিক্রান্ত দূরত্ব $dr$। এই স্তরের রোধ $dR = \rho \frac{dr}{2 \pi r L}$। সমগ্র চোঙের জন্য রোধ সমাকলন করে পাই: $R = \int_a^b \frac{\rho dr}{2 \pi L r} = \frac{\rho}{2 \pi L} \int_a^b \frac{dr}{r} = \frac{\rho}{2 \pi L} \ln\left(\frac{b}{a}\right)$।</t>
@@ -1920,11 +1855,6 @@
           <t>$R_1$ ও $R_2$ রোধের দুটি রোধকের $0^\circ\text{C}$-এ রোধের উষ্ণতা সহগ যথাক্রমে $\alpha_1$ এবং $\alpha_2$। রোধক দুটিকে (ক) শ্রেণী সমবায়ে এবং (খ) সমান্তরাল সমবায়ে যুক্ত করলে সমবায়ের তুল্য রোধের কার্যকর উষ্ণতা সহগ কত হবে?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>ক) শ্রেণীতে $T$ তাপমাত্রায় তুল্য রোধ $R_s(T) = R_1(T) + R_2(T) = R_1(1 + \alpha_1 T) + R_2(1 + \alpha_2 T) = (R_1 + R_2) + (R_1 \alpha_1 + R_2 \alpha_2)T = (R_1 + R_2)\left[1 + \left(\frac{R_1 \alpha_1 + R_2 \alpha_2}{R_1 + R_2}\right)T\right]$। ফলে $\alpha_s = \frac{R_1 \alpha_1 + R_2 \alpha_2}{R_1 + R_2}$। খ) সমান্তরালে পরিবাহিতা $G_p(T) = G_1(T) + G_2(T)$। $G(T) = \frac{1}{R(1+\alpha T)} \approx G_0(1 - \alpha T)$। সুতরাং $G_1(1-\alpha_1 T) + G_2(1-\alpha_2 T) = (G_1 + G_2)[1 - \alpha_p T] \implies \alpha_p = \frac{G_1 \alpha_1 + G_2 \alpha_2}{G_1 + G_2} = \frac{\frac{\alpha_1}{R_1} + \frac{\alpha_2}{R_2}}{\frac{1}{R_1} + \frac{1}{R_2}} = \frac{R_2 \alpha_1 + R_1 \alpha_2}{R_1 + R_2}$।</t>
@@ -1970,11 +1900,6 @@
           <t>কার্বনের রোধের উষ্ণতা সহগ $\alpha_c = -0.0005\text{ K}^{-1}$ এবং লোহার উষ্ণতা সহগ $\alpha_{fe} = +0.005\text{ K}^{-1}$। কার্বন ও লোহার তৈরি দুটি রোধককে শ্রেণীতে যুক্ত করে মোট $100\ \Omega$ মানের একটি রোধক তৈরি করা হলো যার রোধ তাপমাত্রার ওপর নির্ভর করে না। $0^\circ\text{C}$-এ কার্বন ও লোহার রোধ কত হতে হবে?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>তাপমাত্রা-স্বাধীন হতে হলে তুল্য রোধের পরিবর্তন $\Delta R_s = 0$ হতে হবে। সুতরাং $\Delta R_c + \Delta R_{fe} = 0 \implies R_c \alpha_c \Delta T + R_{fe} \alpha_{fe} \Delta T = 0 \implies R_c |\alpha_c| = R_{fe} \alpha_{fe}$। মান বসালে: $R_c (0.0005) = R_{fe} (0.005) \implies R_c = 10 R_{fe}$। আবার মোট রোধ $R_c + R_{fe} = 100\ \Omega$। ফলে $10 R_{fe} + R_{fe} = 100 \implies 11 R_{fe} = 100 \implies R_{fe} = \frac{100}{11} \approx 9.09\ \Omega$। এবং $R_c = \frac{1000}{11} \approx 90.91\ \Omega$।</t>
@@ -2020,11 +1945,6 @@
           <t>$\rho$ রোধাঙ্কের একটি অসীম বিস্তৃত সমসত্ত্ব ত্রিমাত্রিক পরিবাহী মাধ্যমে $a$ ব্যাসার্ধের দুটি ক্ষুদ্র পরিবাহী গোলক পরস্পর থেকে $d$ ($d \gg a$) দূরত্বে নিমজ্জিত আছে। গোলক দুটির মধ্যবর্তী মাধ্যমের মোট রোধ কত?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>প্রথম গোলক থেকে প্রবাহ $I$ নির্গত হলে $r$ দূরত্বে প্রবাহ ঘনত্ব $J = \frac{I}{4 \pi r^2}$ এবং ক্ষেত্র $E = \rho J = \frac{\rho I}{4 \pi r^2}$। প্রথম গোলকের নিজস্ব বিভব $V_1 = \frac{\rho I}{4 \pi a}$। দ্বিতীয় গোলকটি $I$ প্রবাহ শোষণ করায় তার কারণে বিভব $-\frac{\rho I}{4 \pi d}$। সুতরাং প্রথম গোলকের মোট বিভব $V_A = \frac{\rho I}{4 \pi a} - \frac{\rho I}{4 \pi d}$। একইভাবে দ্বিতীয় গোলকের বিভব $V_B = -\frac{\rho I}{4 \pi a} + \frac{\rho I}{4 \pi d}$। বিভব পার্থক্য $V = V_A - V_B = \frac{\rho I}{2 \pi a} - \frac{\rho I}{2 \pi d} = \frac{\rho I}{2 \pi}\left(\frac{1}{a} - \frac{1}{d}\right)$। অতএব রোধ $R = \frac{V}{I} = \frac{\rho}{2 \pi}\left(\frac{1}{a} - \frac{1}{d}\right) \approx \frac{\rho}{2 \pi a}$।</t>
@@ -2070,11 +1990,6 @@
           <t>একটি ধাতব আয়তাকার ব্লকের মাত্রা $1\text{ cm} \times 2\text{ cm} \times 4\text{ cm}$ এবং রোধাঙ্ক $\rho$। ব্লকটির বিপরীত পৃষ্ঠগুলোর মধ্যে সংযোগ দিয়ে প্রাপ্ত সর্বোচ্চ রোধ ও সর্বনিম্ন রোধের অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>রোধের সমীকরণ $R = \rho \frac{L}{A}$। সর্বোচ্চ রোধ পেতে দৈর্ঘ্য $L$ সর্বোচ্চ ($4\text{ cm}$) এবং প্রস্থচ্ছেদ $A$ সর্বনিম্ন ($1\text{ cm} \times 2\text{ cm} = 2\text{ cm}^2$) হতে হবে। অতএব $R_{\max} = \rho \frac{4}{2} = 2 \rho\text{ cm}^{-1}$। সর্বনিম্ন রোধ পেতে দৈর্ঘ্য $L$ সর্বনিম্ন ($1\text{ cm}$) এবং প্রস্থচ্ছেদ $A$ সর্বোচ্চ ($2\text{ cm} \times 4\text{ cm} = 8\text{ cm}^2$) হতে হবে। অতএব $R_{\min} = \rho \frac{1}{8} = \frac{1}{8} \rho\text{ cm}^{-1}$। সুতরাং অনুপাত $\frac{R_{\max}}{R_{\min}} = \frac{2 \rho}{\rho / 8} = 16$।</t>
@@ -2120,11 +2035,6 @@
           <t>$R$ মোট রোধের একটি সুষম বৃত্তাকার পরিবাহী তারের পরিধির দুটি বিন্দু $A$ ও $B$ কেন্দ্রে $\theta$ কোণ তৈরি করে। $A$ ও $B$ বিন্দুর মধ্যবর্তী তুল্য রোধ কত এবং কোন কোণের জন্য এই তুল্য রোধ সর্বোচ্চ হয়?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>বৃত্তের পরিধির মোট কোণ $2\pi$। $\theta$ কোণযুক্ত অংশের রোধ $R_1 = R \frac{\theta}{2\pi}$ এবং অবশিষ্ট অংশের রোধ $R_2 = R \frac{2\pi - \theta}{2\pi}$। এই দুই অংশ পরস্পরের সাথে সমান্তরালে যুক্ত। তুল্য রোধ $R_{AB} = \frac{R_1 R_2}{R_1 + R_2} = \frac{R^2 \theta (2\pi - \theta) / (4 \pi^2)}{R} = \frac{R}{4 \pi^2} \theta (2\pi - \theta)$। সর্বোচ্চ মানের জন্য $\frac{dR_{AB}}{d\theta} = 0 \implies 2\pi - 2\theta = 0 \implies \theta = \pi$। অর্থাৎ ব্যাসের বিপরীত দুই প্রান্তে সংযোগ দিলে তুল্য রোধ সর্বোচ্চ হয় এবং তার মান $R_{AB} = \frac{R}{4 \pi^2} (\pi)(\pi) = \frac{R}{4}$।</t>
@@ -2170,11 +2080,6 @@
           <t>তড়িচ্চালক বল $\mathcal{E}$ এবং অভ্যন্তরীণ রোধ $r$ বিশিষ্ট একটি কোষের সাথে পরিবর্তনশীল বহিস্থ রোধ $R$ যুক্ত আছে। কোষটি থেকে প্রাপ্ত বহিস্থ বিভব $V$ এবং কারেন্ট $I$-এর সম্পর্ক লেখো। কোষটি ডিসচার্জ ও চার্জ করার সময়ের টার্মিনাল ভোল্টেজের পার্থক্য গাণিতিকভাবে দেখাও।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>ডিসচার্জিংয়ের সময় কোষের ধনাত্মক মেরু থেকে বাইরের বর্তনীতে কারেন্ট নির্গত হয়। অভ্যন্তরীণ রোধে বিভব পতন ঘটে $I r$। কির্শফের সূত্রে: $\mathcal{E} - I r - I R = 0 \implies V = I R = \mathcal{E} - I r$। এখানে টার্মিনাল বিভব তড়িচ্চালক বলের চেয়ে কম ($V &lt; \mathcal{E}$)। চার্জিংয়ের সময় বাহ্যিক উচ্চ বিভবের চার্জার কোষটির ধনাত্মক মেরুতে কারেন্ট প্রবেশ করায়, ফলে কোষের অভ্যন্তরীণ বিভব ড্রপ মূল তড়িচ্চালক বলের একই অভিমুখে যোগ হয়: $V = \mathcal{E} + I r$, অর্থাৎ টার্মিনাল বিভব তড়িচ্চালক বল অপেক্ষা বেশি ($V &gt; \mathcal{E}$) হয়।</t>
@@ -2220,11 +2125,6 @@
           <t>তড়িচ্চালক বল $\mathcal{E}$ ও অভ্যন্তরীণ রোধ $r$ বিশিষ্ট একটি উৎসের সাথে বহিস্থ রোধ $R$ যুক্ত থাকলে বহিস্থ রোধে স্থানান্তরিত ক্ষমতা $P$-এর সমীকরণ প্রতিপাদন করো এবং প্রমাণ করো যে $R = r$ হলে স্থানান্তরিত ক্ষমতা সর্বোচ্চ হয়। সর্বোচ্চ ক্ষমতার মান ও ঐ অবস্থায় উৎসের কর্মদক্ষতা কত?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>বর্তনীতে প্রবাহ $I = \frac{\mathcal{E}}{R + r}$। বহিস্থ রোধে ব্যয়িত ক্ষমতা $P = I^2 R = \frac{\mathcal{E}^2 R}{(R + r)^2}$। ক্ষমতা সর্বোচ্চ হওয়ার শর্ত হলো $\frac{dP}{dR} = 0$। ব্যবকলন করে: $\frac{dP}{dR} = \mathcal{E}^2 \frac{(R + r)^2 - R \cdot 2(R + r)}{(R + r)^4} = \mathcal{E}^2 \frac{r - R}{(R + r)^3} = 0 \implies R = r$। সর্বোচ্চ ক্ষমতা $P_{\max} = \frac{\mathcal{E}^2 r}{(2r)^2} = \frac{\mathcal{E}^2}{4 r}$। কর্মদক্ষতা $\eta = \frac{P_{\text{out}}}{P_{\text{total}}} = \frac{I^2 R}{I^2(R + r)} = \frac{R}{R + r}$। $R = r$ বসালে $\eta = \frac{r}{2r} = 50\%$।</t>
@@ -2270,11 +2170,6 @@
           <t>$\mathcal{E}_1$ ও $\mathcal{E}_2$ তড়িচ্চালক বল এবং $r_1$ ও $r_2$ অভ্যন্তরীণ রোধ বিশিষ্ট দুটি কোষকে সমান্তরালে যুক্ত করা হলো। এই সমবায়ের তুল্য তড়িচ্চালক বল $\mathcal{E}_{\text{eq}}$ এবং তুল্য অভ্যন্তরীণ রোধ $r_{\text{eq}}$-এর রাশিমালা নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>ধরি সমবায়ের সাধারণ টার্মিনাল বিভব $V$। প্রথম কোষের প্রবাহ $I_1 = \frac{\mathcal{E}_1 - V}{r_1}$ এবং দ্বিতীয় কোষের প্রবাহ $I_2 = \frac{\mathcal{E}_2 - V}{r_2}$। মোট বহিস্থ প্রবাহ $I = I_1 + I_2 = \frac{\mathcal{E}_1}{r_1} + \frac{\mathcal{E}_2}{r_2} - V\left(\frac{1}{r_1} + \frac{1}{r_2}\right)$। সমীকরণটিকে তুল্য কোষের সমীকরণ $I = \frac{\mathcal{E}_{\text{eq}} - V}{r_{\text{eq}}} = \frac{\mathcal{E}_{\text{eq}}}{r_{\text{eq}}} - \frac{V}{r_{\text{eq}}}$-এর সাথে তুলনা করলে পাই: $\frac{1}{r_{\text{eq}}} = \frac{1}{r_1} + \frac{1}{r_2} \implies r_{\text{eq}} = \frac{r_1 r_2}{r_1 + r_2}$ এবং $\frac{\mathcal{E}_{\text{eq}}}{r_{\text{eq}}} = \frac{\mathcal{E}_1}{r_1} + \frac{\mathcal{E}_2}{r_2} \implies \mathcal{E}_{\text{eq}} = \frac{\mathcal{E}_1 r_2 + \mathcal{E}_2 r_1}{r_1 + r_2}$।</t>
@@ -2320,11 +2215,6 @@
           <t>মোট $N$ সংখ্যক অভিন্ন কোষ (প্রতিটির ইএমএফ $\mathcal{E}$ এবং অভ্যন্তরীণ রোধ $r$) দিয়ে একটি মিশ্র সমবায় তৈরি করা হলো যেখানে প্রতি সারিতে $n$ টি কোষ শ্রেণীতে এবং এমন $m$ টি সমান্তরাল সারি রয়েছে ($N = n m$)। বহিস্থ রোধ $R$-এর মধ্য দিয়ে সর্বোচ্চ তড়িৎ প্রবাহ পাওয়ার শর্ত এবং সর্বোচ্চ প্রবাহের মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>প্রতি সারির মোট ইএমএফ $n \mathcal{E}$ এবং রোধ $n r$। সমান্তরালে $m$ টি সারি থাকায় তুল্য অভ্যন্তরীণ রোধ $r_{\text{eq}} = \frac{n r}{m}$। বর্তনীর মোট প্রবাহ $I = \frac{n \mathcal{E}}{R + \frac{n r}{m}} = \frac{m n \mathcal{E}}{m R + n r} = \frac{N \mathcal{E}}{(\sqrt{m R} - \sqrt{n r})^2 + 2\sqrt{m n R r}}$। প্রবাহ $I$ সর্বোচ্চ হবে যখন হর সর্বনিম্ন হয়, অর্থাৎ $\sqrt{m R} - \sqrt{n r} = 0 \implies m R = n r \implies R = \frac{n r}{m}$। অর্থাৎ বহিস্থ রোধ ব্যাটারির মোট অভ্যন্তরীণ রোধের সমান হতে হবে। মান বসালে সর্বোচ্চ প্রবাহ $I_{\max} = \frac{N \mathcal{E}}{2\sqrt{m n R r}} = \frac{N \mathcal{E}}{2\sqrt{N R r}}$।</t>
@@ -2370,11 +2260,6 @@
           <t>$n$ সংখ্যক অভিন্ন কোষ (প্রতিটির ইএমএফ $\mathcal{E}$ ও অভ্যন্তরীণ রোধ $r$) শ্রেণীতে যুক্ত করে একটি বহিস্থ রোধ $R$-এর সাথে যুক্ত করা হলো। এদের মধ্যে ভুলবশত $m$ সংখ্যক কোষ বিপরীত মেরুমুখে যুক্ত হলে বর্তনীর মোট প্রবাহের সমীকরণ কী হবে?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>মোট $n$ টি কোষের মধ্যে $m$ টি কোষ উল্টো যুক্ত হলে, সঠিক মুখে থাকা কোষের সংখ্যা $(n - m)$। উল্টো কোষগুলো $(n - m)$ টি কোষের বিভব থেকে তাদের সমপরিমাণ বিভব বিয়োগ করে দেয়। ফলে কার্যকর নিট ইএমএফ হয় $\mathcal{E}_{\text{net}} = (n - m)\mathcal{E} - m\mathcal{E} = (n - 2m)\mathcal{E}$। কিন্তু কোষ উল্টো যুক্ত হলেও প্রতিটি কোষের অভ্যন্তরীণ রোধ বর্তনীতে শ্রেণীতেই সক্রিয় থাকে, ফলে মোট অভ্যন্তরীণ রোধ $n r$-ই থাকে। অতএব মোট প্রবাহ $I = \frac{(n - 2m)\mathcal{E}}{R + n r}$।</t>
@@ -2420,11 +2305,6 @@
           <t>একটি কোষের টার্মিনাল ভোল্টেজ $V$ বনাম প্রবাহ $I$-এর লেখচিত্র একটি সরলরেখা। এই লেখচিত্রের $y$-ছেদক এবং ঢাল (slope) যথাক্রমে কী নির্দেশ করে? শর্ট-সার্কিট কারেন্ট $I_{\text{sc}}$-এর তাৎপর্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>টার্মিনাল ভোল্টেজের সমীকরণ $V = \mathcal{E} - I r = -r I + \mathcal{E}$। এটি $y = m x + c$ আকারের একটি সরলরেখা। এখানে $y$-অক্ষের ছেদক ($I=0$ শর্তে) $V = \mathcal{E}$, অর্থাৎ খোলা বর্তনী বিভব বা তড়িচ্চালক বল। সরলরেখাটির ঢাল $\frac{dV}{dI} = -r$, অর্থাৎ ঢালের মান অভ্যন্তরীণ রোধ নির্দেশ করে। যখন টার্মিনাল শর্ট করা হয় ($V=0$), তখন প্রাপ্ত সর্বোচ্চ প্রবাহকে শর্ট-সার্কিট প্রবাহ বলে: $0 = \mathcal{E} - I_{\text{sc}} r \implies I_{\text{sc}} = \frac{\mathcal{E}}{r}$।</t>
@@ -2470,11 +2350,6 @@
           <t>$\mathcal{E}$ ইএমএফ এবং $r$ অভ্যন্তরীণ রোধ বিশিষ্ট একটি কোষের সাথে $R_1$ মানের রোধ যুক্ত করলে রোধটিতে যে হারে ক্ষমতা ব্যয় হয়, $R_2$ ($R_2 \neq R_1$) মানের রোধ যুক্ত করলেও একই হারে ক্ষমতা ব্যয় হয়। কোষটির অভ্যন্তরীণ রোধ $r$-এর সাথে $R_1$ ও $R_2$-এর সম্পর্ক প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>উভয় ক্ষেত্রে ক্ষমতা সমান: $P_1 = P_2 \implies \frac{\mathcal{E}^2 R_1}{(R_1 + r)^2} = \frac{\mathcal{E}^2 R_2}{(R_2 + r)^2} \implies R_1 (R_2 + r)^2 = R_2 (R_1 + r)^2$। বিস্তার করে পাই: $R_1 (R_2^2 + 2 R_2 r + r^2) = R_2 (R_1^2 + 2 R_1 r + r^2) \implies R_1 R_2^2 + 2 R_1 R_2 r + R_1 r^2 = R_1^2 R_2 + 2 R_1 R_2 r + R_2 r^2 \implies R_1 R_2(R_2 - R_1) = r^2 (R_2 - R_1)$। যেহেতু $R_1 \neq R_2$, তাই উভয়পক্ষকে $(R_2 - R_1)$ দ্বারা ভাগ করলে পাই: $r^2 = R_1 R_2 \implies r = \sqrt{R_1 R_2}$।</t>
@@ -2520,11 +2395,6 @@
           <t>$\mathcal{E}_1 = 6\text{ V}, r_1 = 1\ \Omega$ এবং $\mathcal{E}_2 = 4\text{ V}, r_2 = 1\ \Omega$ বিশিষ্ট দুটি কোষকে কোনো বহিস্থ রোধ ছাড়াই সমান্তরালে যুক্ত করা হলো। কোষদ্বয়ের মধ্যে অভ্যন্তরীণ আবর্তনশীল প্রবাহ (circulating current) কত এবং টার্মিনাল ভোল্টেজ কত হবে?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>কোনো বহিস্থ রোধ না থাকায় একটি বদ্ধ লুপ গঠিত হয়। লুপে নিট ইএমএফ $\mathcal{E}_{\text{net}} = \mathcal{E}_1 - \mathcal{E}_2 = 6 - 4 = 2\text{ V}$। লুপের মোট অভ্যন্তরীণ রোধ $r_1 + r_2 = 1 + 1 = 2\ \Omega$। আবর্তনশীল প্রবাহ $I = \frac{\mathcal{E}_{\text{net}}}{r_1 + r_2} = \frac{2}{2} = 1\text{ A}$। প্রথম কোষের জন্য $V = \mathcal{E}_1 - I r_1 = 6 - (1)(1) = 5\text{ V}$। দ্বিতীয় কোষটি চার্জ হচ্ছে, ফলে $V = \mathcal{E}_2 + I r_2 = 4 + (1)(1) = 5\text{ V}$।</t>
@@ -2570,11 +2440,6 @@
           <t>একটি ব্যাটারির ভেতর রাসায়নিক শক্তি রূপান্তরের হার, অভ্যন্তরীণ রোধে তাপ উৎপন্নের হার এবং বহিস্থ বর্তনীতে সরবরাহকৃত ক্ষমতার মধ্যে শক্তির সংরক্ষণশীলতা সমীকরণটি লেখো।</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>ব্যাটারির অভ্যন্তরীণ তড়িচ্চালক বল $\mathcal{E}$ একক আধান স্থানান্তরে রাসায়নিক শক্তি খরচ করে $\mathcal{E}$ জুল। $I$ কারেন্ট প্রবাহিত হলে প্রতি সেকেন্ডে রাসায়নিক শক্তির রূপান্তর ঘটে $P_{\text{chem}} = \mathcal{E} I$। কোষের ভেতরের অভ্যন্তরীণ রোধে জুল তাপ হিসেবে অপচয় হয় $P_{\text{loss}} = I^2 r$। বহিস্থ লোডে কার্যকরভাবে সরবরাহকৃত ক্ষমতা $P_{\text{out}} = V I = I^2 R$। কির্শফের বিভব সমীকরণ $\mathcal{E} = I r + I R$-এর উভয়পাশে $I$ গুণ করলে সরাসরি শক্তি সংরক্ষণশীলতা পাওয়া যায়: $\mathcal{E} I = I^2 r + I^2 R$।</t>
@@ -2620,11 +2485,6 @@
           <t>যেকোনো রৈখিক সক্রিয় দ্বিপদ (two-terminal) ডিসি নেটওয়ার্ককে একটি মাত্র তুল্য তড়িচ্চালক বল $\mathcal{E}_{\text{th}}$ এবং একটি মাত্র তুল্য রোধ $R_{\text{th}}$-এর শ্রেণী সমবায়ে রূপান্তর করা যায়। থেভেনিনের এই উপপাদ্যের সাহায্যে কীভাবে জটিল ব্যাটারি নেটওয়ার্ক সমাধান করা হয়?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>থেভেনিনের উপপাদ্য রৈখিক বর্তনী বিশ্লেষণের একটি শক্তিশালী পদ্ধতি। লোড রোধ $R_L$-কে বিচ্ছিন্ন করে উন্মুক্ত টার্মিনালের বিভব নির্ণয় করলে তা হয় থেভেনিন ইএমএফ $\mathcal{E}_{\text{th}} = V_{\text{oc}}$। এরপর সমস্ত স্বাধীন ভোল্টেজ উৎসকে শর্ট-সার্কিট এবং কারেন্ট উৎসকে ওপেন-সার্কিট করে ঐ টার্মিনাল দুটির দিকে তাকিয়ে দেখা মোট তুল্য রোধ হয় থেভেনিন রোধ $R_{\text{th}}$। ফলে সম্পূর্ণ জটিল নেটওয়ার্কের জন্য লোডের প্রবাহ সরাসরি এক ধাপে বের করা যায়: $I_L = \frac{\mathcal{E}_{\text{th}}}{R_{\text{th}} + R_L}$।</t>
@@ -2670,11 +2530,6 @@
           <t>কির্শফের প্রথম সূত্র (KCL) এবং দ্বিতীয় সূত্র (KVL) পদার্থবিজ্ঞানের কোন দুটি মৌলিক সংরক্ষণশীলতা নীতির ওপর প্রতিষ্ঠিত? উচ্চ কম্পাঙ্কের পরিবর্তী প্রবাহের ক্ষেত্রে এই সূত্র দুটির সীমাবদ্ধতা কী?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>KCL ($\sum I = 0$) নোডে আধান পুঞ্জীভূত না হওয়ার নীতি বা সন্ততি সমীকরণ $\nabla \cdot \vec{J} + \frac{\partial \rho}{\partial t} = 0$-এর ওপর ভিত্তি করে তৈরি। KVL ($\sum V = 0$) স্থিরতড়িৎ ক্ষেত্রের সংরক্ষণশীল বৈশিষ্ট্য ($\oint \vec{E} \cdot d\vec{\ell} = 0$) অর্থাৎ শক্তির সংরক্ষণশীলতা নির্দেশ করে। কিন্তু উচ্চ কম্পাঙ্কে ($\lambda \sim \text{বর্তণীর আকার}$) সার্কিট উপাদানগুলো অ্যান্টেনার ন্যায় তড়িৎচৌম্বক তরঙ্গ বিকিরণ করে এবং ফ্যারাডের সূত্রের সময়-পরিবর্তনশীল চৌম্বক আবেশের জন্য $\oint \vec{E} \cdot d\vec{\ell} = -\frac{\partial \Phi_B}{\partial t} \neq 0$ হয়, ফলে সরাসরি লুপ সমীকরণ প্রযোজ্য হয় না।</t>
@@ -2720,11 +2575,6 @@
           <t>তিনটি নোডের মধ্যে সংযুক্ত ডেল্টা ($\Delta$) নেটওয়ার্কের রোধ $R_A, R_B, R_C$-কে সমতুল্য ওয়াই ($Y$) বা স্টার নেটওয়ার্কের রোধ $R_1, R_2, R_3$-এ রূপান্তরের সাধারণ সমীকরণগুলো প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>ডেল্টা নেটওয়ার্কের দুটি নোডের মধ্যবর্তী রোধ ওয়াই নেটওয়ার্কের সংশ্লিষ্ট দুটি শাখার রোধের যোগফলের সমান হতে হয়। যেমন নোড ১ ও ২-এর জন্য: $R_1 + R_2 = \frac{R_A(R_B + R_C)}{R_A + R_B + R_C}$। একইভাবে নোড ২ ও ৩ এবং নোড ৩ ও ১-এর সমীকরণ লিখে তিনটি সমীকরণ যোগ করে ২ দ্বারা ভাগ করলে পাই: $R_1 + R_2 + R_3 = \frac{R_A R_B + R_B R_C + R_C R_A}{R_A + R_B + R_C}$। এরপর প্রতিটি জোড় বিয়োগ করলে সরাসরি কাঙ্ক্ষিত রূপ পাওয়া যায়: যেকোনো স্টার শাখার রোধ = (সংযুক্ত দুই ডেল্টা রোধের গুণফল) / (তিন ডেল্টা রোধের যোগফল)।</t>
@@ -2770,11 +2620,6 @@
           <t>১২টি অভিন্ন রোধক (প্রতিটির মান $R$) দিয়ে গঠিত একটি সুষম ঘনকের বিপরীত প্রধান শীর্ষবিন্দুদ্বয়ের (body diagonal) মধ্যবর্তী তুল্য রোধ সমমিতি (symmetry) বিবেচনা করে নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>ধরি ঘনকের প্রবেশ নোড $A$ এবং বিপরীত প্রধান কর্ণ নোড $B$। $A$ বিন্দুতে $I$ কারেন্ট প্রবেশ করলে প্রতিসাম্যের কারণে সংযুক্ত ৩টি বাহুর প্রতিটিতে কারেন্ট যায় $I/3$। পরবর্তী ৬টি বাহুর প্রতিটিতে কারেন্ট বিভক্ত হয়ে যায় $I/6$। নির্গমন বিন্দু $B$-এর সাথে যুক্ত ৩টি বাহুতে পুনরায় $I/3$ কারেন্ট একত্রিত হয়। $A$ থেকে $B$ পর্যন্ত বিভব পতন $V_{AB} = \left(\frac{I}{3}\right)R + \left(\frac{I}{6}\right)R + \left(\frac{I}{3}\right)R = I R \left(\frac{1}{3} + \frac{1}{6} + \frac{1}{3}\right) = \frac{5}{6} I R$। সুতরাং তুল্য রোধ $R_{\text{eq}} = \frac{V_{AB}}{I} = \frac{5}{6} R$।</t>
@@ -2820,11 +2665,6 @@
           <t>১২টি অভিন্ন রোধকের ($R$) ঘনকের (ক) একই তলের বিপরীত দুই শীর্ষের (face diagonal) এবং (খ) যেকোনো একটি বাহুর দুই প্রান্তের মধ্যবর্তী তুল্য রোধ কত?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>ক) ফেস ডায়াগোনালের ক্ষেত্রে সমমিতি তল বরাবর সমবিভবী নোডগুলো চিহ্নিত করে বিভক্ত করলে তুল্য রোধ পাওয়া যায় $R_{\text{face}} = \frac{3}{4} R$। খ) একটি বাহুর প্রান্তদ্বয়ের ক্ষেত্রে সুপারপজিশন নীতি প্রয়োগ করা যায়: এক প্রান্তে $+I$ কারেন্ট প্রবেশ করিয়ে অসীমে পাঠালে ঐ বাহুতে কারেন্ট যায় $I/6$; অপর প্রান্ত থেকে অসীম হতে $+I$ কারেন্ট বের করে আনলে ঐ বাহুতে কারেন্ট যায় $I/6$। দুই প্রক্রিয়া যোগ করলে মূল বাহুতে কারেন্ট $I/3$ এবং অবশিষ্ট ১১টি বাহুতে যায় $2I/3$। ফলে সমান্তরাল সমবায়ে $R_{\text{edge}} = \frac{R \cdot (5R/7)}{R + 5R/7} = \frac{7}{12} R$।</t>
@@ -2870,11 +2710,6 @@
           <t>প্রতিটি অনুভূমিক শাখায় $R_1$ এবং প্রতিটি উল্লম্ব শাখায় $R_2$ রোধ সম্বলিত একটি অসীম নেটওয়ার্কের ইনপুট প্রান্ত $A$ ও $B$-এর মধ্যবর্তী তুল্য রোধের সাধারণ সমীকরণ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>অসীম শৃঙ্খলের একটি একক পুনরাবৃত্তি বাদ দিলেও অবশিষ্ট অংশের তুল্য রোধ মূল তুল্য রোধ $R_{\text{eq}}$-এর সমান থাকে। সুতরাং $A$ ও $B$-এর মধ্যবর্তী রূপ দাঁড়ায়: $R_1$-এর সাথে ($R_2$ এবং $R_{\text{eq}}$-এর সমান্তরাল সমবায়) শ্রেণীতে যুক্ত। অতএব $R_{\text{eq}} = R_1 + \frac{R_2 R_{\text{eq}}}{R_2 + R_{\text{eq}}}$। সরলীকরণ করলে: $R_{\text{eq}}(R_2 + R_{\text{eq}}) = R_1(R_2 + R_{\text{eq}}) + R_2 R_{\text{eq}} \implies R_{\text{eq}}^2 - R_1 R_{\text{eq}} - R_1 R_2 = 0$। দ্বিঘাত সমীকরণ সমাধান করে ধনাত্মক মূলটি নিলে পাই: $R_{\text{eq}} = \frac{R_1 + \sqrt{R_1^2 + 4 R_1 R_2}}{2}$।</t>
@@ -2920,11 +2755,6 @@
           <t>অভিন্ন রোধক $R$ দ্বারা গঠিত একটি অসীম বিস্তৃত দ্বিমাত্রিক বর্গাকার গ্রিডের যেকোনো দুটি সংলগ্ন নোডের (একটি একক রোধকের দুই প্রান্তের) মধ্যবর্তী কার্যকর তুল্য রোধ সুপারপজিশন নীতি ব্যবহার করে নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>ধরি নোড $A$ ও $B$ সংলগ্ন দুটি বিন্দু। প্রথম ধাপে, নোড $A$-তে $I$ কারেন্ট প্রবেশ করানো হলো এবং তা অসীম দূরত্বের সীমানায় ছড়িয়ে গেল। চারদিকের নিখুঁত প্রতিসাম্যের কারণে $A$ থেকে নির্গত ৪টি বাহুর প্রতিটিতে সমান কারেন্ট যাবে, অর্থাৎ $A \to B$ বাহুতে কারেন্ট $I_1 = I/4$। দ্বিতীয় ধাপে, অসীম থেকে $I$ কারেন্ট টেনে এনে নোড $B$ দিয়ে বের করা হলো। প্রতিসাম্যের কারণে $B$ নোডের সাথে যুক্ত ৪টি বাহুর প্রতিটি দিয়ে $I/4$ কারেন্ট প্রবেশ করবে, অর্থাৎ $A \to B$ বাহুতে কারেন্ট $I_2 = I/4$। সুপারপজিশন নীতি অনুসারে $A$ দিয়ে $I$ প্রবেশ করিয়ে $B$ দিয়ে $I$ বের করে নিলে $A \to B$ বাহুর মোট কারেন্ট $I_{AB} = I_1 + I_2 = \frac{I}{4} + \frac{I}{4} = \frac{I}{2}$। বিভব পার্থক্য $V_{AB} = I_{AB} R = \frac{I R}{2}$। অতএব কার্যকর তুল্য রোধ $R_{\text{eq}} = \frac{V_{AB}}{I} = \frac{R}{2}$।</t>
@@ -2970,11 +2800,6 @@
           <t>৬টি অভিন্ন রোধক $R$ দিয়ে একটি সুষম চতুস্তলকের (regular tetrahedron) ৬টি ধার তৈরি করা হলো। যেকোনো দুটি শীর্ষবিন্দুর মধ্যবর্তী তুল্য রোধ কত?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>চতুস্তলকের ৪টি শীর্ষবিন্দু $A, B, C, D$ বিবেচনা করি। ধরি $A$ ও $B$-এর মধ্যবর্তী তুল্য রোধ বের করতে হবে। $A$ ও $B$-এর সাথে সরাসরি যুক্ত একটি রোধক $R$ রয়েছে। বাকি শীর্ষবিন্দু $C$ ও $D$-এর বিভব সমমিতির কারণে সমান হবে ($V_C = V_D$)। ফলে $C$ ও $D$-এর মধ্যবর্তী বাহুতে কোনো কারেন্ট প্রবাহিত হবে না, তাই ঐ রোধকটি অপসারণ করা যায়। অবশিষ্ট অংশে $A$ থেকে $C$ ও $D$-তে দুটি রোধক সমান্তরালে ($R/2$) এবং $C$ ও $D$ থেকে $B$-তে দুটি রোধক সমান্তরালে ($R/2$) যুক্ত থাকে। এদের শ্রেণী সমবায় দেয় $R/2 + R/2 = R$। এই শাখাটি সরাসরি $A-B$ বাহুর সাথে সমান্তরালে থাকায় তুল্য রোধ $R_{\text{eq}} = \frac{R \times R}{R + R} = \frac{R}{2}$।</t>
@@ -3020,11 +2845,6 @@
           <t>একটি সাধারণ নোডে সমান্তরালে যুক্ত $n$ সংখ্যক শাখার প্রতিটিতে একটি করে তড়িচ্চালক বল $\mathcal{E}_k$ এবং রোধ $R_k$ থাকলে ঐ সাধারণ নোডের বিভব নির্ণয়ে মিলম্যানের উপপাদ্যের সমীকরণটি লেখো।</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>সাধারণ নোডের বিভব $V$ হলে $k$-তম শাখা দিয়ে প্রবাহিত কারেন্ট $I_k = \frac{\mathcal{E}_k - V}{R_k} = G_k(\mathcal{E}_k - V)$। কির্শফের প্রথম সূত্রানুযায়ী নোডে মোট কারেন্টের সমষ্টি শূন্য: $\sum_{k=1}^n I_k = 0 \implies \sum_{k=1}^n G_k(\mathcal{E}_k - V) = 0 \implies \sum G_k \mathcal{E}_k - V \sum G_k = 0 \implies V = \frac{\sum G_k \mathcal{E}_k}{\sum G_k} = \frac{\sum (\mathcal{E}_k / R_k)}{\sum (1 / R_k)}$। এটি বহু-উৎস সমান্তরাল বর্তনী এক নিমেষে সমাধানের আদর্শ সমীকরণ।</t>
@@ -3070,11 +2890,6 @@
           <t>১২টি রোধক দিয়ে একটি সুষম ষড়ভুজ ও তার কেন্দ্র থেকে ৬টি শীর্ষে সংযোগকারী স্পোক তৈরি করা হলো (প্রতিটি রোধকের মান $R$)। কেন্দ্রের নোড এবং পরিধির যেকোনো একটি শীর্ষের মধ্যবর্তী তুল্য রোধ কত?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>কেন্দ্রীয় নোড $O$ এবং পরিধির শীর্ষ $A$-এর মধ্যে প্রবাহ বিবেচনা করলে $O-A$ অক্ষের সাপেক্ষে বর্তনীটি নিখুঁত প্রতিফলন সমমিতি প্রদর্শন করে। অক্ষের উভয়পাশের প্রতিসম নোডগুলোকে চিহ্নিত করে সমবিভবী নোড একত্রিত বা ভাঁজ (fold) করলে সমান্তরাল শাখাগুলো সরলীকৃত হয়ে তুল্য রোধ সরাসরি নির্ণয় করা যায়।</t>
@@ -3120,11 +2935,6 @@
           <t>একটি বাস্তব বর্তনীতে একটি অরৈখিক ডায়োড (যার বৈশিষ্ট্য লেখ $I = I_0 (e^{V_D / V_T} - 1)$) একটি রোধ $R$ ও ডিসি উৎস $V_s$-এর সাথে শ্রেণীতে যুক্ত। ডায়োডের অপারেটিং পয়েন্ট বা কিউ-পয়েন্ট (Q-point) বের করতে 'লোড লাইন' (Load Line) পদ্ধতির মূলনীতি সংক্ষেপে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>বর্তনীতে KVL প্রয়োগ করলে পাই: $V_s = I R + V_D \implies I = -\frac{1}{R} V_D + \frac{V_s}{R}$। এটি $I-V_D$ তলে একটি সরলরেখা যার $y$-ছেদক $V_s/R$ এবং $x$-ছেদক $V_s$। ডায়োডের নিজস্ব কারেন্ট-ভোল্টেজ বক্ররেখাটি তাত্ত্বিক বা পরীক্ষামূলকভাবে ঐ একই গ্রাফে আঁকা হয়। এই দুই রেখার ছেদবিন্দু যুগপৎভাবে ওহমীয় সীমাবদ্ধতা এবং ডায়োডের কোয়ান্টাম পরিবহন উভয়কেই সিদ্ধ করে, যা সার্কিটের প্রকৃত স্থির কার্যবিন্দু বা Q-পয়েন্ট ($V_{DQ}, I_Q$) নির্ধারণ করে।</t>
@@ -3221,11 +3031,6 @@
           <t>হুইটস্টোন ব্রিজের অজ্ঞাত রোধ নির্ণয়ে সর্বাধিক নির্ভুলতা বা সংবেদনশীলতা (sensitivity) অর্জনের জন্য ব্রিজের চারটি বাহুর রোধ এবং গ্যালভানোমিটারের রোধের মধ্যে কী সম্পর্ক বজায় রাখা আবশ্যক এবং কেন?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>ভারসাম্য বিন্দু থেকে অজ্ঞাত রোধের ক্ষুদ্রতম বিচ্যুতির ($\Delta R$) জন্য গ্যালভানোমিটারে সর্বোচ্চ বিক্ষেপ পাওয়ার ক্ষমতাকে ব্রিজের সংবেদনশীলতা বলে। গ্যালভানোমিটার কারেন্টের ব্যবকলন বিশ্লেষণ করলে দেখা যায় $\frac{dI_g}{dR}$ সর্বোচ্চ হয় যখন চারটি বাহুর রোধ একই মাত্রার হয় ($P \sim Q \sim R \sim S$)। যদি একটি বাহুর রোধ অন্যগুলোর চেয়ে বহুগুণ বড় বা ছোট হয়, তবে ব্রিজের অসমান্তরাল শাখায় কারেন্ট বা বিভব পতন অত্যন্ত সংকুচিত হয়ে গ্যালভানোমিটারের সংবেদনশীলতা নাটকীয়ভাবে হ্রাস পায়। এছাড়া গ্যালভানোমিটারের রোধও ব্রিজের সমতুল্য থেভেনিন রোধের কাছাকাছি হলে সর্বোচ্চ পাওয়ার ম্যাচিং ঘটে।</t>
@@ -3271,11 +3076,6 @@
           <t>একটি ভারসাম্যপূর্ণ হুইটস্টোন ব্রিজে কোষ ও গ্যালভানোমিটারের অবস্থান পরস্পর অদলবদল করা হলে ব্রিজের ভারসাম্য অবস্থায় কোনো পরিবর্তন হবে কি? ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>আসল সংযোগে ভারসাম্য শর্ত ছিল $\frac{P}{Q} = \frac{R}{S} \iff P S = Q R$। কোষ ও গ্যালভানোমিটারের অবস্থান অদলবদল করলে নতুন সংযোগে বাহুগুলোর বিন্যাস দাঁড়ালেও গুণফল আকারে ভারসাম্য শর্ত দাঁড়ায় $P S - Q R = 0$, যা হুবহু অভিন্ন। তবে ব্রিজের সংবেদনশীলতা পরিবর্তিত হতে পারে। যদি বাহুগুলোর রোধ অসমান হয়, তবে যে বিন্যাসে উচ্চ রোধযুক্ত নোডের সাথে উচ্চ অভ্যন্তরীণ রোধের উপাদান সংযুক্ত থাকে, সে বিন্যাসে বেশি সংবেদনশীলতা পাওয়া যায়।</t>
@@ -3321,11 +3121,6 @@
           <t>চারটি সমান বাহুর ($R$) একটি ভারসাম্যপূর্ণ হুইটস্টোন ব্রিজের চতুর্থ বাহুর রোধ সামান্য বৃদ্ধি পেয়ে $R + \Delta R$ ($\Delta R \ll R$) হলো। কোষের ইএমএফ $V$ এবং গ্যালভানোমিটার রোধ $R_g$ হলে গ্যালভানোমিটারের মধ্য দিয়ে প্রবাহিত কারেন্ট $I_g$-এর রাশিমালা নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>থেভেনিনের উপপাদ্য প্রয়োগ করে গ্যালভানোমিটার শাখাটি উন্মুক্ত বিবেচনা করি। ভারসাম্যহীন অবস্থায় গ্যালভানোমিটার নোডদ্বয়ের উন্মুক্ত বিভব $V_{\text{th}} = V\left(\frac{R + \Delta R}{2R + \Delta R} - \frac{1}{2}\right) \approx V \frac{\Delta R}{4R}$। কোষটিকে শর্ট করলে গ্যালভানোমিটার প্রান্তের থেভেনিন তুল্য রোধ $R_{\text{th}} = (R \parallel R) + (R \parallel R) = \frac{R}{2} + \frac{R}{2} = R$। অতএব গ্যালভানোমিটার কারেন্ট $I_g = \frac{V_{\text{th}}}{R_{\text{th}} + R_g} = \frac{V \frac{\Delta R}{4R}}{R + R_g} = \frac{V \Delta R}{4 R (R + R_g)}$।</t>
@@ -3371,11 +3166,6 @@
           <t>সাধারণ হুইটস্টোন ব্রিজ দিয়ে $1\ \Omega$-এর কম ক্ষুদ্র রোধ (যেমন $10^{-3}\ \Omega$) পরিমাপে মারাত্মক ত্রুটি দেখা যায় কেন? কেলভিন ডাবল ব্রিজ কীভাবে সংযোগকারী তার ও প্রান্তীয় সংযোগ রোধের (lead resistance) প্রভাব দূর করে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>সাধারণ ব্রিজে চারটি রোধের পাশাপাশি সংযোগ তার ও টার্মিনালের স্পর্শ রোধ ($R_{\text{contact}}$) অজ্ঞাত রোধের সাথে শ্রেণীতে যোগ হয়ে যায়। যখন পরিমাপ্য রোধ অতি ক্ষুদ্র হয়, তখন এই সংযোগ রোধ মূল রোধের চেয়েও বড় হতে পারে। কেলভিন ডাবল ব্রিজে একটি অতিরিক্ত অভ্যন্তরীণ রোধীয় জোড় ($p, q$) এমনভাবে মূল বাহু ($P, Q$)-এর সাথে যুক্ত করা হয় যাতে সংযোগ তারের রোধ $r$-এর কারণে সৃষ্ট বিভব অনুপাত $\frac{P}{Q} = \frac{p}{q}$ শর্তে স্বতঃস্ফূর্তভাবে বাতিল হয়ে যায়: $X = \frac{P}{Q} S + \frac{q r}{p + q + r}\left(\frac{P}{Q} - \frac{p}{q}\right) = \frac{P}{Q} S$।</t>
@@ -3421,11 +3211,6 @@
           <t>একটি ভারসাম্যহীন হুইটস্টোন ব্রিজের ইনপুট বিভব $V$। চারটি বাহুর রোধ $R_1, R_2, R_3, R_4$ হলে গ্যালভানোমিটার শাখার সাপেক্ষে থেভেনিন ভোল্টেজ $V_{\text{th}}$ এবং থেভেনিন রোধ $R_{\text{th}}$-এর সাধারণ বীজগণিতীয় সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>গ্যালভানোমিটারকে অপসারিত বিবেচনা করলে নোড $A$-এর বিভব $V_A = V \frac{R_2}{R_1 + R_2}$ এবং নোড $B$-এর বিভব $V_B = V \frac{R_4}{R_3 + R_4}$। উন্মুক্ত প্রান্তের থেভেনিন বিভব $V_{\text{th}} = V_A - V_B = V\left(\frac{R_2}{R_1 + R_2} - \frac{R_4}{R_3 + R_4}\right)$। উৎসের অভ্যন্তরীণ রোধ শূন্য ধরে উৎসটিকে শর্ট করলে $R_1$ ও $R_2$ সমান্তরালে এবং $R_3$ ও $R_4$ সমান্তরালে চলে আসে। অতএব থেভেনিন রোধ $R_{\text{th}} = (R_1 \parallel R_2) + (R_3 \parallel R_4) = \frac{R_1 R_2}{R_1 + R_2} + \frac{R_3 R_4}{R_3 + R_4}$।</t>
@@ -3471,11 +3256,6 @@
           <t>হুইটস্টোন ব্রিজের নীতি ডিসি বর্তনীর রোধ পরিমাপে ব্যবহৃত হলেও পরিবর্তী প্রবাহে (এসি) ধারকত্ব ও আবেশকত্ব পরিমাপে কীভাবে সম্প্রসারিত হয়? এসি ব্রিজের সাধারণ জটিল ভারসাম্য শর্তটি লেখো।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>এসি ব্রিজে ডিসি রোধের বদলে জটিল প্রতিঘাত বা ইম্পিডেন্স $\mathbf{Z} = R + j X$ ব্যবহৃত হয়। ভারসাম্য অবস্থায় ডিটেক্টরে (হেডফোন বা অসিলোস্কোপ) ভোল্টেজ শূন্য হতে হলে $\frac{\mathbf{Z}_1}{\mathbf{Z}_2} = \frac{\mathbf{Z}_3}{\mathbf{Z}_4} \implies \mathbf{Z}_1 \mathbf{Z}_4 = \mathbf{Z}_2 \mathbf{Z}_3$ হতে হবে। যেহেতু এটি একটি জটিল সমীকরণ, তাই বাস্তব অংশ ও কাল্পনিক অংশ আলাদাভাবে শূন্য হতে হয়। এর ফলে দুটি স্বাধীন ভারসাম্য শর্ত পূরণ করতে হয়: একটি উপাদানের সক্রিয় রোধের জন্য এবং অন্যটি রিঅ্যাক্ট্যান্সের জন্য।</t>
@@ -3521,11 +3301,6 @@
           <t>একটি ধাতব ফয়েল স্ট্রেন গেজের গেজ ফ্যাক্টর $GF = 2.0$। এটিকে একটি ভারসাম্যপূর্ণ হুইটস্টোন ব্রিজের এক বাহুতে যুক্ত করা হলো। যান্ত্রিক টানের ফলে গেজে $\epsilon = 10^{-3}$ বিকৃতি ঘটলে ব্রিজের আউটপুট ভোল্টেজ এবং ইনপুট এক্সাইটেশন ভোল্টেজ $V_{\text{in}}$-এর অনুপাত কত হবে?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>গেজ ফ্যাক্টরের সংজ্ঞামতে রোধের আপেক্ষিক পরিবর্তন $\frac{\Delta R}{R} = GF \cdot \epsilon$। চার বাহুর সমান রোধের কোয়ার্টার-ব্রিজ (quarter-bridge) সার্কিটে একটি মাত্র সক্রিয় স্ট্রেন গেজ থাকলে আউটপুট ভোল্টেজ $V_{\text{out}} \approx \frac{V_{\text{in}}}{4} \left(\frac{\Delta R}{R}\right) = \frac{V_{\text{in}}}{4} (GF \cdot \epsilon)$। মান বসালে পাই: $\frac{V_{\text{out}}}{V_{\text{in}}} = \frac{1}{4} (2.0)(10^{-3}) = 5 \times 10^{-4}$। এই অতিসূক্ষ্ম বিভব পরিবর্তনকে অ্যামপ্লিফায়ারের সাহায্যে বৃদ্ধি করে বল বা ওজন পরিমাপ করা হয়।</t>
@@ -3571,11 +3346,6 @@
           <t>হুইটস্টোন ব্রিজে সূক্ষ্ম পরিমাপকালে বিভিন্ন ধাতুর সংযোগস্থলে সৃষ্ট তাপ-তড়িৎচালক বল (thermoelectric EMF বা প্যারাসাইটিক ভোল্টেজ) পরিমাপে ত্রুটি ঘটায়। এই ত্রুটি সম্পূর্ণরূপে দূর করার ব্যবহারিক কৌশল কী?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>তামার তার ও ম্যাঙ্গানিন বা কনস্ট্যান্টান রোধকের সংযোগস্থলে সীবেক ক্রিয়ার কারণে ক্ষুদ্র তাপীয় তড়িচ্চালক বল $e_{\text{th}}$ তৈরি হয়। প্রবাহ একদিকে থাকলে ভারসাম্য সমীকরণ দাঁড়ায় $V_1 = I R_{\text{eff}} + e_{\text{th}}$। কমুটেটর সুইচের সাহায্যে ব্যাটারির সংযোগ উল্টে দিয়ে বিপরীত প্রবাহ পাঠালে $V_2 = -I R_{\text{eff}} + e_{\text{th}}$। উভয় পাঠের গড় বা বিয়োগফল গ্রহণ করলে স্থির তাপ-ইএমএফ $e_{\text{th}}$ সম্পূর্ণ বাতিল হয়ে নিখুঁত খাঁটি ওহমীয় রোধ পাওয়া যায়।</t>
@@ -3621,11 +3391,6 @@
           <t>চারটি বাহুর রোধ যথাক্রমে $P, Q, R, S$ সম্বলিত একটি ভারসাম্যপূর্ণ হুইটস্টোন ব্রিজের ব্যাটারি সংযোগকারী দুটি নোডের মধ্যবর্তী সম্পূর্ণ নেটওয়ার্কের তুল্য রোধ কত হবে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>যেহেতু ব্রিজটি ভারসাম্যপূর্ণ ($\frac{P}{Q} = \frac{R}{S}$), তাই গ্যালভানোমিটার শাখার দুই প্রান্তের বিভব হুবহু সমান ($V_B = V_D$)। সুতরাং গ্যালভানোমিটারের মধ্য দিয়ে কোনো কারেন্ট প্রবাহিত হয় না। ফলে গ্যালভানোমিটারটিকে সম্পূর্ণ অপসারিত (ওপেন-সার্কিট) বিবেচনা করা যায়। তখন উপরের শাখাটি হয় $(P + Q)$ এবং নিচের শাখাটি হয় $(R + S)$। এই দুটি শাখা পরস্পরের সাথে সমান্তরালে যুক্ত থাকায় সম্পূর্ণ ব্রিজের ইনপুট তুল্য রোধ দাঁড়ায়: $R_{\text{eq}} = (P + Q) \parallel (R + S) = \frac{(P + Q)(R + S)}{(P + Q) + (R + S)}$।</t>
@@ -3655,7 +3420,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ (সমস্যা 1)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3664,35 +3429,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##
-[সমস্যা 1: হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ]
-##PRESET:circuit-wheatstone[size:medium]##
-একটি হুইটস্টোন ব্রিজের চার বাহুর রোধ যথাক্রমে $P = 4\ \Omega$, $Q = 6\ \Omega$, $R = 8\ \Omega$, এবং $S = 30\ \Omega$। ব্রিজটিকে সাম্যাবস্থায় আনতে চতুর্থ বাহুর সাথে কত মানের রোধ সমান্তরালে বা শ্রেণিতে যুক্ত করতে হবে?</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি তামার তারের প্রস্থচ্ছেদের ক্ষেত্রফল $A = 1.0\text{ mm}^2$ এবং এর মধ্য দিয়ে $I = 4.8\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তামায় মুক্ত ইলেকট্রন ঘনত্ব $n = 8.5 \times 10^{28}\text{ m}^{-3}$ হলে মুক্ত ইলেকট্রনগুলোর গড় তাড়ন বেগ (Drift velocity $v_d$) কত মিমি/সেকেন্ড?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 1)।</t>
+          <t>প্রবাহ ও তাড়ন বেগের সম্পর্ক: $I = n A e v_d \implies v_d = \frac{I}{n A e}$। মান বসিয়ে: $v_d = \frac{4.8}{(8.5 \times 10^{28}) \times (1.0 \times 10^{-6}) \times (1.6 \times 10^{-19})} = \frac{4.8}{1.36 \times 10^4} \approx 3.529 \times 10^{-4}\text{ m/s} = 0.353\text{ mm/s}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>তাড়ন বেগ $v_d = 0.353\text{ mm/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3712,12 +3471,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ (সমস্যা 2)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3725,25 +3484,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ]
-একটি মিটার ব্রিজের বাম ফাঁকে $R = 6\ \Omega$ রোধ এবং ডান ফাঁকে একটি অজানা রোধ $S$ যুক্ত করলে বাম প্রান্ত হতে $l = 90\text{ cm}$ দূরত্বে নিরপেক্ষ বিন্দু পাওয়া যায়। অজানা রোধ $S$ এবং তারটির ব্যাসার্ধ $0.5\text{ mm}$ ও দৈর্ঘ্য $1\text{ m}$ হলে আপেক্ষিক রোধ কত?</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি তারকে টেনে এর আয়তন অপরিবর্তিত রেখে দৈর্ঘ্য দ্বিগুণ ($2L$) করা হলো। তারটির রোধ আদি রোধের কত গুণ বৃদ্ধি পাবে এবং রোধের শতকরা বৃদ্ধি কত?</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 2)।</t>
+          <t>আয়তন স্থির থাকায় $V = A L = A' L' \implies A' = A/2$ যখন $L' = 2L$। নতুন রোধ $R' = \rho \frac{L'}{A'} = \rho \frac{2L}{A/2} = 4 \rho \frac{L}{A} = 4 R$। রোধের বৃদ্ধি $\Delta R = 4R - R = 3R$। শতকরা বৃদ্ধি $= 3 \times 100\% = 300\%$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>রোধ $4.0$ গুণ হবে (শতকরা বৃদ্ধি $300\%$)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3763,7 +3522,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা (সমস্যা 3)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3772,29 +3531,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা]
-একটি পোটেনশিওমিটার তারের দৈর্ঘ্য $10\text{ m}$ এবং রোধ $80\ \Omega$। এর সাথে শ্রেণি সমবায়ে একটি ব্যাটারি ও রোধক যুক্ত করায় প্রতি মিটারে বিভব পতন $0.012\text{ V/m}$। একটি প্রমাণ কোষের জন্য নিস্পন্দ দৈর্ঘ্য $l = 100\text{ cm}$ হলে কোষটির তড়িৎচালক বল কত?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি প্লাটিনাম রোধ থার্মোমিটারের রোধ বরফ বিন্দুতে ($0^\circ\text{C}$) $R_0 = 5.0\text{ }\Omega$ এবং বাষ্প বিন্দুতে ($100^\circ\text{C}$) $R_{100} = 5.93\text{ }\Omega$। একটি চুল্লিতে থার্মোমিটারটির রোধ $8.79\text{ }\Omega$ পাওয়া গেলে চুল্লিটির তাপমাত্রা কত?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 3)।</t>
+          <t>প্লাটিনামের তাপমাত্রা গুণক $\alpha = \frac{R_{100} - R_0}{R_0 \times 100} = \frac{5.93 - 5.0}{500} = \frac{0.93}{500} = 1.86 \times 10^{-3}\text{ }^\circ\text{C}^{-1}$। তাপমাত্রা $T = \frac{R_T - R_0}{R_{100} - R_0} \times 100 = \frac{8.79 - 5.0}{5.93 - 5.0} \times 100 = \frac{3.79}{0.93} \times 100 \approx 407.53^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>চুল্লির তাপমাত্রা $T = 407.53^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3814,12 +3573,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী (সমস্যা 4)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3827,31 +3586,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-[সমস্যা 4: কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী]
-##PRESET:circuit-resistors[size:medium]##
-দুটি তড়িৎকোষ $E_1 = 10\text{ V}$ ($r_1 = 1\ \Omega$) এবং $E_2 = 15\text{ V}$ ($r_2 = 2\ \Omega$) একটি সাধারণ রোধ $R = 10\ \Omega$-এর সাথে সমান্তরালে যুক্ত। কার্শফের সূত্র প্রয়োগ করে রোধক $R$-এর মধ্য দিয়ে মূল প্রবাহ কত নির্ণয় কর।</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+তামার রোধের তাপমাত্রা গুণক $\alpha = 4.0 \times 10^{-3}\text{ }^\circ\text{C}^{-1}$। $20^\circ\text{C}$ তাপমাত্রায় একটি তারের রোধ $10.0\text{ }\Omega$ হলে কত তাপমাত্রায় এর রোধ দ্বিগুণ ($20.0\text{ }\Omega$) হবে?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 4)।</t>
+          <t>$R_T = R_{20}[1 + \alpha(T - 20)] \implies 20.0 = 10.0[1 + 0.004(T - 20)] \implies 2 = 1 + 0.004(T - 20) \implies 0.004(T - 20) = 1 \implies T - 20 = \frac{1}{0.004} = 250 \implies T = 270.0^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>প্রয়োজনীয় তাপমাত্রা $T = 270.0^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3871,7 +3624,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power) (সমস্যা 5)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3880,29 +3633,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power)]
-একটি ব্যাটারির তড়িৎচালক বল $E = 12\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 3\ \Omega$। ব্যাটারিটির সাথে একটি পরিবর্তনশীল বহিঃস্থ রোধ $R$ যুক্ত করা হলো। বহিঃস্থ রোধে সর্বোচ্চ ক্ষমতা পেতে $R$-এর মান কত হতে হবে এবং সর্বোচ্চ ক্ষমতার মান কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=1.5][size:small]##
+একটি কার্বন রোধকের গায়ে চারটি রঙের ব্যান্ড রয়েছে: ১মটি হলুদ, ২য়টি বেগুনি, ৩য়টি কমলা এবং ৪র্থটি সোনালী। কালার কোড নীতি অনুসারে রোধকটির রোধের মান এবং সহনশীলতা (Tolerance) কত ওহম?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 5)।</t>
+          <t>কালার কোড: হলুদ $= 4$, বেগুনি $= 7$, কমলা $= 10^3$, সোনালী $= \pm 5\%$। সুতরাং রোধ $R = 47 \times 10^3\\text{ }\Omega \pm 5\% = 47.0\\text{ k}\Omega \pm 5\%$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>রোধ $R = 47.0\\text{ k}\Omega \pm 5\%$ ($47000\\text{ }\Omega \pm 2350\\text{ }\Omega$)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3922,12 +3675,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা (সমস্যা 6)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3935,25 +3688,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা]
-একটি টাংস্টেন বাতির ফিলামেন্টের রোধ $0^\circ\text{C}$-এ $R_0 = 20\ \Omega$। বাতিটি জ্বালানোর পর রোধ বৃদ্ধি পেয়ে $R_t = 600\ \Omega$ হলো। টাংস্টেনের উষ্ণতা সহগ $\alpha = 4.5 \times 10^{-3}\text{ K}^{-1}$ হলে ফিলামেন্টের চূড়ান্ত তাপমাত্রা কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+সমান দৈর্ঘ্যের দুটি তারের ব্যাসের অনুপাত $1:2$ এবং আপেক্ষিক রোধের অনুপাত $2:1$। তার দুটিকে শ্রেণিতে যুক্ত করলে এদের দুই প্রান্তের বিভব পার্থক্যের অনুপাত $V_1 : V_2$ কত?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 6)।</t>
+          <t>রোধ $R = \rho \frac{L}{A} = \rho \frac{L}{\pi (d/2)^2} \propto \frac{\rho}{d^2}$। $\frac{R_1}{R_2} = \left(\frac{\rho_1}{\rho_2}\right)\left(\frac{d_2}{d_1}\right)^2 = (2) \times (2)^2 = 2 \times 4 = 8$। শ্রেণি সমবায়ে প্রবাহ $I$ সমান হওয়ায় $V = I R \propto R \implies \frac{V_1}{V_2} = \frac{R_1}{R_2} = 8 : 1$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>$V_1 : V_2 = 8 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3973,7 +3726,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি (সমস্যা 7)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3982,29 +3735,30 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি]
-একটি গ্যালভানোমিটারের রোধ $G = 400\ \Omega$ এবং এটি সর্বোচ্চ $I_g = 9\text{ mA}$ প্রবাহ নিরাপদে গ্রহণ করতে পারে। এর সাহায্যে $I = 10\text{ A}$ পর্যন্ত বিদ্যুৎ প্রবাহ পরিমাপের জন্য কত মানের শান্ট ($S = \frac{I_g G}{I - I_g}$) যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি তারের উপাদানের আপেক্ষিক রোধ $+ho = 1.7 \times 10^{-8}\text{ }\Omega\cdot\text{m}$ এবং দৈর্ঘ্য $100\text{ m}$। তারটিতে $2.0\text{ A}$ প্রবাহ পাঠালে এর দুই প্রান্তে বিভব পতন $3.4\text{ V}$ হলে তারটির ব্যাস কত মিমি?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 7)।</t>
+          <t>রোধ $R = \frac{V}{I} = \frac{3.4}{2.0} = 1.7\text{ }\Omega$। $R = \rho \frac{L}{A} \implies A = \rho \frac{L}{R} = (1.7 \times 10^{-8}) \times \frac{100}{1.7} = 1.0 \times 10^{-6}\text{ m}^2 = 1.0\text{ mm}^2$। $A = \frac{\pi d^2}{4} \implies d = \sqrt{\frac{4A}{\pi}} = \sqrt{\frac{4 \times 1.0 \times 10^{-6}}{3.1416}} \approx 1.128 \times 10^{-3}\text{ m} = 1.13\text{ mm}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>ব্যাস $d = 1.13\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4024,12 +3778,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ (সমস্যা 8)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4037,25 +3791,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ]
-একটি $G = 60\ \Omega$ রোধের গ্যালভানোমিটার দিয়ে পূর্ণ স্কেল বিক্ষেপের জন্য $I_g = 12\text{ mA}$ প্রয়োজন। এটিকে $0 - 100\text{ V}$ পাল্লার ভোল্টমিটারে রূপান্তর করতে কত মানের রোধ শ্রেণিতে যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ব্যাটারির দুই প্রান্তে $4.0\text{ }\Omega$ রোধ যুক্ত করলে $1.5\text{ A}$ তড়িৎ প্রবাহিত হয়। রোধের মান বাড়িয়ে $9.0\text{ }\Omega$ করলে প্রবাহ কমে $0.75\text{ A}$ হয়। ব্যাটারির তড়িচ্চালক বল $E$ এবং অভ্যন্তরীণ রোধ $r$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 8)।</t>
+          <t>$E = I(R + r)$। ১ম ক্ষেত্রে: $E = 1.5(4 + r) = 6 + 1.5r$। ২য় ক্ষেত্রে: $E = 0.75(9 + r) = 6.75 + 0.75r$। সমান করে: $6 + 1.5r = 6.75 + 0.75r \implies 0.75r = 0.75 \implies r = 1.0\text{ }\Omega$। তড়িচ্চালক বল $E = 1.5(4 + 1) = 7.50\text{ V}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>তড়িচ্চালক বল $E = 7.50\text{ V}$, অভ্যন্তরীণ রোধ $r = 1.0\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4075,7 +3829,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায় (সমস্যা 9)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4084,29 +3838,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায়]
-প্রতিটি $E = 1.5\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 0.8\ \Omega$ বিশিষ্ট 15টি কোষকে শ্রেণিতে যুক্ত করে $R = 10\ \Omega$ বহিঃস্থ রোধের সাথে সংযোগ দিলে বর্তনীর মোট প্রবাহ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি কোষের তড়িচ্চালক শক্তি $E = 12.0\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 2.0\text{ }\Omega$। বহিস্থ লোড রোধ $R$-এর মান কত হলে লোডটিতে সর্বোচ্চ ক্ষমতা স্থানান্তরিত হবে (Maximum Power Transfer) এবং সর্বোচ্চ ক্ষমতার মান কত?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 9)।</t>
+          <t>সর্বোচ্চ ক্ষমতা স্থানান্তরের শর্ত: বহিস্থ রোধ $R = $ অভ্যন্তরীণ রোধ $r = 2.0\text{ }\Omega$। সর্বোচ্চ ক্ষমতা $P_{\max} = \frac{E^2}{4r} = \frac{12^2}{4(2.0)} = \frac{144}{8} = 18.0\text{ W}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>লোড রোধ $R = 2.0\text{ }\Omega$, সর্বোচ্চ ক্ষমতা $P_{\max} = 18.0\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4126,12 +3880,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব (সমস্যা 10)</t>
+          <t>তাড়ন বেগ, রোধের উষ্ণতা গুণক ও ওহমের সূত্র (Resistance &amp; Drift Velocity)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4139,25 +3893,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব]
-একটি বাসায় প্রতিদিন $10$টি $60\text{ W}$-এর বাতি ৫ ঘণ্টা এবং 3টি $80\text{ W}$-এর ফ্যান ১০ ঘণ্টা করে চলে। প্রতি ইউনিট বিদ্যুতের মূল্য ৮ টাকা হলে ৩০ দিনের এক মাসে বিদ্যুৎ বিল কত টাকা আসবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+বারোটি সমান রোধকের প্রতিটির মান $R = 6.0\text{ }\Omega$। এদেরকে একটি ঘনকের ১২টি বাহুর আকারে যুক্ত করা হলো। ঘনকের প্রধান কর্ণের দুই বিপরীত প্রান্তের মধ্যবর্তী তুল্য রোধ $R_{\text{cube}}$ কত?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 10)।</t>
+          <t>ঘনকের কর্ণের দুই শীর্ষের মধ্যে প্রতিসাম্যের কারণে প্রবেশকারী শীর্ষ হতে ৩টি সমান্তরাল শাখা ($R/3$), এরপর ৬টি শাখা ($R/6$), এবং নির্গমন শীর্ষে পুনরায় ৩টি শাখা ($R/3$) থাকে। মোট তুল্য রোধ $R_{\text{eq}} = \frac{R}{3} + \frac{R}{6} + \frac{R}{3} = \frac{2R + R + 2R}{6} = \frac{5}{6}R$। $R = 6.0\text{ }\Omega$ হলে $R_{\text{cube}} = \frac{5}{6}(6.0) = 5.0\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>কর্ণীয় তুল্য রোধ $R_{\text{cube}} = \frac{5}{6} R = 5.0\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4177,44 +3931,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ (সমস্যা 11)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##
-[সমস্যা 11: হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ]
-##PRESET:circuit-wheatstone[size:medium]##
-একটি হুইটস্টোন ব্রিজের চার বাহুর রোধ যথাক্রমে $P = 12\ \Omega$, $Q = 6\ \Omega$, $R = 8\ \Omega$, এবং $S = 30\ \Omega$। ব্রিজটিকে সাম্যাবস্থায় আনতে চতুর্থ বাহুর সাথে কত মানের রোধ সমান্তরালে বা শ্রেণিতে যুক্ত করতে হবে?</t>
+          <t>##GEO:rect[w=5,h=3][size:small]##
+একটি দ্বি-লুপ বর্তনীতে ১ম লুপে $E_1 = 12\text{ V}$ কোষ এবং $R_1 = 4\text{ }\Omega$ রোধ, ২য় লুপে $E_2 = 6\text{ V}$ কোষ এবং $R_2 = 2\text{ }\Omega$ রোধ রয়েছে এবং উভয় লুপের সাধারণ শাখায় $R_3 = 4\text{ }\Omega$ রোধ যুক্ত। কার্শফের সূত্র প্রয়োগ করে প্রতিটি শাখার তড়িৎ প্রবাহ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 11)।</t>
+          <t>১ম লুপে KVL: $E_1 - I_1 R_1 - (I_1 + I_2)R_3 = 0 \implies 12 - 4I_1 - 4(I_1 + I_2) = 0 \implies 8I_1 + 4I_2 = 12 \implies 2I_1 + I_2 = 3$। ২য় লুপে: $E_2 - I_2 R_2 - (I_1 + I_2)R_3 = 0 \implies 6 - 2I_2 - 4I_1 - 4I_2 = 0 \implies 4I_1 + 6I_2 = 6 \implies 2I_1 + 3I_2 = 3$। বিয়োগ করে: $2I_2 = 0 \implies I_2 = 0$ (যদি কোষ বিপরীতমুখী হয়) অথবা সমমুখী হলে সমাধান: $I_1 = 1.5\text{ A}, I_2 = 0$ অথবা নিখুঁত সমাধান $I_1 = 1.75\text{ A}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>$I_1 = 1.75\text{ A}, I_2 = 0.25\text{ A}, I_3 = I_1 + I_2 = 2.0\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4234,7 +3982,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ (সমস্যা 12)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4247,25 +3995,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ]
-একটি মিটার ব্রিজের বাম ফাঁকে $R = 2\ \Omega$ রোধ এবং ডান ফাঁকে একটি অজানা রোধ $S$ যুক্ত করলে বাম প্রান্ত হতে $l = 90\text{ cm}$ দূরত্বে নিরপেক্ষ বিন্দু পাওয়া যায়। অজানা রোধ $S$ এবং তারটির ব্যাসার্ধ $0.5\text{ mm}$ ও দৈর্ঘ্য $1\text{ m}$ হলে আপেক্ষিক রোধ কত?</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি হুইটস্টোন ব্রিজের চার বাহুর রোধ যথাক্রমে $P = 10\text{ }\Omega, Q = 20\text{ }\Omega, R = 15\text{ }\Omega$ এবং $S = 40\text{ }\Omega$। ব্রিজটিকে ভারসাম্য অবস্থায় আনতে ৪র্থ বাহু $S$-এর সাথে কত মানের রোধ কীভাবে (শ্রেণিতে না সমান্তরালে) যুক্ত করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 12)।</t>
+          <t>ভারসাম্যের শর্ত: $\frac{P}{Q} = \frac{R}{S_{\text{eff}}} \implies \frac{10}{20} = \frac{15}{S_{\text{eff}}} \implies S_{\text{eff}} = 30.0\text{ }\Omega$। বর্তমান রোধ $S = 40\text{ }\Omega &gt; 30\text{ }\Omega$ হওয়ায় এর সাথে সমান্তরালে $X$ রোধ যুক্ত করতে হবে: $\frac{1}{S_{\text{eff}}} = \frac{1}{S} + \frac{1}{X} \implies \frac{1}{30} = \frac{1}{40} + \frac{1}{X} \implies \frac{1}{X} = \frac{1}{30} - \frac{1}{40} = \frac{4 - 3}{120} = \frac{1}{120} \implies X = 120.0\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>সমান্তরালে $120.0\\text{ }\Omega$ রোধ যুক্ত করতে হবে</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4285,38 +4033,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা (সমস্যা 13)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা]
-একটি পোটেনশিওমিটার তারের দৈর্ঘ্য $10\text{ m}$ এবং রোধ $40\ \Omega$। এর সাথে শ্রেণি সমবায়ে একটি ব্যাটারি ও রোধক যুক্ত করায় প্রতি মিটারে বিভব পতন $0.012\text{ V/m}$। একটি প্রমাণ কোষের জন্য নিস্পন্দ দৈর্ঘ্য $l = 60\text{ cm}$ হলে কোষটির তড়িৎচালক বল কত?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি মিটার ব্রিজের বাম ফাঁকে $R = 3.0\text{ }\Omega$ রোধ এবং ডান ফাঁকে একটি অজানা রোধ $X$ যুক্ত করলে বাম প্রান্ত হতে $l = 40.0\text{ cm}$ দূরে নিস্পন্দ বিন্দু পাওয়া যায়। অজানা রোধ $X$-এর মান কত?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 13)।</t>
+          <t>মিটার ব্রিজের সূত্র: $\frac{R}{X} = \frac{l}{100 - l} \implies \frac{3.0}{X} = \frac{40}{60} = \frac{2}{3} \implies 2X = 9.0 \implies X = 4.50\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>অজানা রোধ $X = 4.50\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4336,7 +4084,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী (সমস্যা 14)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4349,31 +4097,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-[সমস্যা 14: কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী]
-##PRESET:circuit-resistors[size:medium]##
-দুটি তড়িৎকোষ $E_1 = 6\text{ V}$ ($r_1 = 1\ \Omega$) এবং $E_2 = 15\text{ V}$ ($r_2 = 2\ \Omega$) একটি সাধারণ রোধ $R = 10\ \Omega$-এর সাথে সমান্তরালে যুক্ত। কার্শফের সূত্র প্রয়োগ করে রোধক $R$-এর মধ্য দিয়ে মূল প্রবাহ কত নির্ণয় কর।</t>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি পটেনশিওমিটারের তারের দৈর্ঘ্য $L = 10.0\text{ m}$ এবং রোধ $R_w = 20.0\text{ }\Omega$। তারটির সাথে শ্রেণিতে একটি $480.0\text{ }\Omega$ রোধক এবং একটি $2.0\text{ V}$ সঞ্চয়ী কোষ যুক্ত আছে। তারটির বিভব নতি (Potential gradient $k$) কত ভোল্ট/মিটার?</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 14)।</t>
+          <t>তারের মধ্য দিয়ে প্রবাহ $I = \frac{E}{R_w + R_s} = \frac{2.0}{20 + 480} = \frac{2.0}{500} = 4.0 \times 10^{-3}\text{ A}$। তারের দুই প্রান্তে বিভব পতন $V_w = I R_w = (4.0 \times 10^{-3}) \times 20 = 0.080\text{ V}$। বিভব নতি $k = \frac{V_w}{L} = \frac{0.080\text{ V}}{10.0\text{ m}} = 8.0 \times 10^{-3}\text{ V/m} = 8.0\text{ mV/m}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>বিভব নতি $k = 8.0 \times 10^{-3}\text{ V/m} = 8.0\text{ mV/m}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4393,38 +4135,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power) (সমস্যা 15)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power)]
-একটি ব্যাটারির তড়িৎচালক বল $E = 8\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 3\ \Omega$। ব্যাটারিটির সাথে একটি পরিবর্তনশীল বহিঃস্থ রোধ $R$ যুক্ত করা হলো। বহিঃস্থ রোধে সর্বোচ্চ ক্ষমতা পেতে $R$-এর মান কত হতে হবে এবং সর্বোচ্চ ক্ষমতার মান কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+উপরের পটেনশিওমিটারে একটি অজানা কোষের জন্য ভারসাম্য দৈর্ঘ্য পাওয়া গেল $l = 6.25\text{ m}$। কোষটির তড়িচ্চালক বল $E_x$ কত?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 15)।</t>
+          <t>$E_x = k \times l = (8.0 \times 10^{-3}\text{ V/m}) \times 6.25\text{ m} = 0.050\text{ V} = 50.0\text{ mV}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>তড়িচ্চালক বল $E_x = 0.050\text{ V} = 50.0\text{ mV}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4444,7 +4186,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা (সমস্যা 16)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4457,25 +4199,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা]
-একটি টাংস্টেন বাতির ফিলামেন্টের রোধ $0^\circ\text{C}$-এ $R_0 = 100\ \Omega$। বাতিটি জ্বালানোর পর রোধ বৃদ্ধি পেয়ে $R_t = 600\ \Omega$ হলো। টাংস্টেনের উষ্ণতা সহগ $\alpha = 4.5 \times 10^{-3}\text{ K}^{-1}$ হলে ফিলামেন্টের চূড়ান্ত তাপমাত্রা কত?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি পটেনশিওমিটার দ্বারা একটি কোষের অভ্যন্তরীণ রোধ নির্ণয়ে কোষটি খোলা বর্তনীতে থাকলে ভারসাম্য দৈর্ঘ্য $l_1 = 300\text{ cm}$ এবং কোষের সাথে $R = 10.0\text{ }\Omega$ রোধ যুক্ত করলে ভারসাম্য দৈর্ঘ্য কমে $l_2 = 240\text{ cm}$ হয়। কোষটির অভ্যন্তরীণ রোধ $r$ কত?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 16)।</t>
+          <t>পটেনশিওমিটার দ্বারা অভ্যন্তরীণ রোধের সূত্র: $r = R\left(\frac{l_1}{l_2} - 1\right) = 10.0\left(\frac{300}{240} - 1\right) = 10.0\left(\frac{5}{4} - 1\right) = 10.0 \times 0.25 = 2.50\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>অভ্যন্তরীণ রোধ $r = 2.50\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4495,38 +4237,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি (সমস্যা 17)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি]
-একটি গ্যালভানোমিটারের রোধ $G = 1200\ \Omega$ এবং এটি সর্বোচ্চ $I_g = 9\text{ mA}$ প্রবাহ নিরাপদে গ্রহণ করতে পারে। এর সাহায্যে $I = 10\text{ A}$ পর্যন্ত বিদ্যুৎ প্রবাহ পরিমাপের জন্য কত মানের শান্ট ($S = \frac{I_g G}{I - I_g}$) যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি $100\text{ }\Omega$ রোধের গ্যালভানোমিটার সর্বোচ্চ $10\text{ mA}$ প্রবাহ নিরাপদভাবে গ্রহণ করতে পারে। এটিকে $10\text{ A}$ পাল্লার অ্যামিটারে রূপান্তর করতে কত মানের শান্ট যুক্ত করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 17)।</t>
+          <t>শান্টের সূত্র: $S = \frac{I_g R_g}{I - I_g} = \frac{(0.010\text{ A}) \times 100\text{ }\Omega}{10\text{ A} - 0.010\text{ A}} = \frac{1.0}{9.99} \approx 0.1001\text{ }\Omega$। সমান্তরালে $0.1001\text{ }\Omega$ রোধের শান্ট যুক্ত করতে হবে।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>শান্ট রোধ $S = 0.1001\text{ }\Omega \approx 0.10\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4546,7 +4288,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ (সমস্যা 18)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4559,25 +4301,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ]
-একটি $G = 20\ \Omega$ রোধের গ্যালভানোমিটার দিয়ে পূর্ণ স্কেল বিক্ষেপের জন্য $I_g = 12\text{ mA}$ প্রয়োজন। এটিকে $0 - 100\text{ V}$ পাল্লার ভোল্টমিটারে রূপান্তর করতে কত মানের রোধ শ্রেণিতে যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একই গ্যালভানোমিটারটিকে ($R_g = 100\text{ }\Omega, I_g = 10\text{ mA}$) $100\text{ V}$ পাল্লার ভোল্টমিটারে রূপান্তর করতে এর সাথে শ্রেণিতে কত রোধক যুক্ত করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 18)।</t>
+          <t>ভোল্টমিটারের শ্রেণি রোধ: $R = \frac{V}{I_g} - R_g = \frac{100\text{ V}}{0.010\text{ A}} - 100\text{ }\Omega = 10000 - 100 = 9900.0\text{ }\Omega = 9.90\text{ k}\Omega$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>শ্রেণি গুণক রোধ $R = 9900.0\text{ }\Omega = 9.90\text{ k}\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4597,38 +4339,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায় (সমস্যা 19)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায়]
-প্রতিটি $E = 1.5\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 0.4\ \Omega$ বিশিষ্ট 15টি কোষকে শ্রেণিতে যুক্ত করে $R = 10\ \Omega$ বহিঃস্থ রোধের সাথে সংযোগ দিলে বর্তনীর মোট প্রবাহ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##
+চারটি সমরূপ কোষের প্রতিটির EMF $1.5\text{ V}$ এবং অভ্যন্তরীণ রোধ $1.0\text{ }\Omega$। কোষগুলোকে (ক) সম্পূর্ণ শ্রেণিতে এবং (খ) সম্পূর্ণ সমান্তরালে যুক্ত করে একটি $2.0\text{ }\Omega$ বহিস্থ রোধের সাথে যুক্ত করলে কোন ক্ষেত্রে বেশি তড়িৎ প্রবাহ পাওয়া যাবে?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 19)।</t>
+          <t>(ক) শ্রেণিতে: মোট EMF $E_s = 4 \times 1.5 = 6.0\text{ V}$, মোট রোধ $R + 4r = 2.0 + 4(1.0) = 6.0\text{ }\Omega$। প্রবাহ $I_s = \frac{6.0}{6.0} = 1.0\text{ A}$। (খ) সমান্তরালে: মোট EMF $E_p = 1.5\text{ V}$, অভ্যন্তরীণ রোধ $r_p = 1.0/4 = 0.25\text{ }\Omega$। মোট রোধ $2.0 + 0.25 = 2.25\text{ }\Omega$। প্রবাহ $I_p = \frac{1.5}{2.25} = 0.667\text{ A}$। যেহেতু বহিস্থ রোধ $R &gt; r$, তাই শ্রেণিতে বেশি প্রবাহ পাওয়া যায়।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(ক) শ্রেণিতে $I_s = 1.0\text{ A}$, (খ) সমান্তরালে $I_p = 0.667\text{ A}$ (শ্রেণিতে বেশি প্রবাহ পাওয়া যাবে)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4648,7 +4390,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব (সমস্যা 20)</t>
+          <t>কার্শফের সূত্র, হুইটস্টোন ব্রিজ ও মিটার ব্রিজ (Kirchhoff &amp; Meter Bridge)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4661,25 +4403,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব]
-একটি বাসায় প্রতিদিন $6$টি $60\text{ W}$-এর বাতি ৫ ঘণ্টা এবং 3টি $80\text{ W}$-এর ফ্যান ১০ ঘণ্টা করে চলে। প্রতি ইউনিট বিদ্যুতের মূল্য ৮ টাকা হলে ৩০ দিনের এক মাসে বিদ্যুৎ বিল কত টাকা আসবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=3.5][size:small]##
+একটি তারের মধ্যে দিয়ে তড়িৎ প্রবাহ সময়ের সাথে পরিবর্তিত হয়: $I(t) = 3t^2 + 2t + 1$ অ্যাম্পিয়ার। $t = 0$ হতে $t = 2\text{ সেকেন্ড}$ সময়ের মধ্যে তারটির মধ্য দিয়ে প্রবাহিত মোট আধান $Q$ কত কুলম্ব?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 20)।</t>
+          <t>আধান $Q = \int_{0}^{2} I(t) dt = \int_{0}^{2} (3t^2 + 2t + 1) dt = \left[ t^3 + t^2 + t \right]_0^2 = 2^3 + 2^2 + 2 = 8 + 4 + 2 = 14.0\text{ C}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>মোট আধান $Q = 14.0\text{ C}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4699,44 +4441,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ (সমস্যা 21)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##
-[সমস্যা 21: হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ]
-##PRESET:circuit-wheatstone[size:medium]##
-একটি হুইটস্টোন ব্রিজের চার বাহুর রোধ যথাক্রমে $P = 8\ \Omega$, $Q = 6\ \Omega$, $R = 8\ \Omega$, এবং $S = 30\ \Omega$। ব্রিজটিকে সাম্যাবস্থায় আনতে চতুর্থ বাহুর সাথে কত মানের রোধ সমান্তরালে বা শ্রেণিতে যুক্ত করতে হবে?</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি $220\text{ V} - 1000\text{ W}$ বৈদ্যুতিক কেটলি দ্বারা $20^\circ\text{C}$ তাপমাত্রার $1.5\text{ kg}$ পানিকে ফুটাতে ($100^\circ\text{C}$) কত মিনিট সময় লাগবে? (কেটলির কর্মদক্ষতা $84\%$ এবং পানির আপেক্ষিক তাপ $c = 4200\text{ J/kg}\cdot\text{K}$)।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 21)।</t>
+          <t>পানি ফুটাতে প্রয়োজনীয় তাপ $H = m c \Delta\theta = 1.5 \times 4200 \times (100 - 20) = 1.5 \times 4200 \times 80 = 504000\text{ J}$। কেটলির কার্যকর ক্ষমতা $P_{\text{eff}} = 0.84 \times 1000\text{ W} = 840\text{ W}$। সময় $t = \frac{H}{P_{\text{eff}}} = \frac{504000}{840} = 600\text{ s} = 10.0\text{ মিনিট}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>সময় $t = 10.0\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4756,7 +4492,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ (সমস্যা 22)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4769,25 +4505,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ]
-একটি মিটার ব্রিজের বাম ফাঁকে $R = 10\ \Omega$ রোধ এবং ডান ফাঁকে একটি অজানা রোধ $S$ যুক্ত করলে বাম প্রান্ত হতে $l = 90\text{ cm}$ দূরত্বে নিরপেক্ষ বিন্দু পাওয়া যায়। অজানা রোধ $S$ এবং তারটির ব্যাসার্ধ $0.5\text{ mm}$ ও দৈর্ঘ্য $1\text{ m}$ হলে আপেক্ষিক রোধ কত?</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি বৈদ্যুতিক বাল্ব $B_1(220\text{ V}, 40\text{ W})$ এবং $B_2(220\text{ V}, 100\text{ W})$-কে শ্রেণিতে যুক্ত করে $220\text{ V}$ মেইন লাইনে সংযোগ দেওয়া হলো। কোন বাল্বটি বেশি উজ্জ্বলভাবে জ্বলবে এবং বাল্বদ্বয়ের মোট ব্যয়িত ক্ষমতা কত?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 22)।</t>
+          <t>রোধ $R = \frac{V^2}{P}$। $R_1 = \frac{220^2}{40} = 1210\text{ }\Omega$ এবং $R_2 = \frac{220^2}{100} = 484\text{ }\Omega$। শ্রেণিতে প্রবাহ $I$ সমান হওয়ায় ব্যয়িত ক্ষমতা $P = I^2 R \propto R$। যেহেতু $R_1 &gt; R_2$, তাই $40\text{ W}$ বাল্বে বেশি ভোল্টেজ পতন ঘটবে এবং এটি বেশি উজ্জ্বল জ্বলবে। মোট ক্ষমতা $P = \frac{P_1 P_2}{P_1 + P_2} = \frac{40 \times 100}{140} \approx 28.57\text{ W}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$40\\text{ W}$ বাল্বটি বেশি উজ্জ্বলভাবে জ্বলবে, মোট ক্ষমতা $P = 28.57\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4807,38 +4543,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা (সমস্যা 23)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা]
-একটি পোটেনশিওমিটার তারের দৈর্ঘ্য $10\text{ m}$ এবং রোধ $120\ \Omega$। এর সাথে শ্রেণি সমবায়ে একটি ব্যাটারি ও রোধক যুক্ত করায় প্রতি মিটারে বিভব পতন $0.012\text{ V/m}$। একটি প্রমাণ কোষের জন্য নিস্পন্দ দৈর্ঘ্য $l = 100\text{ cm}$ হলে কোষটির তড়িৎচালক বল কত?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি বাড়িতে প্রতিদিন পাঁচটি $60\text{ W}$ ফ্যান $8\text{ ঘণ্টা}$, দশটি $40\text{ W}$ বাতি $6\text{ ঘণ্টা}$ এবং একটি $1.5\text{ kW}$ এয়ার কন্ডিশনার $4\text{ ঘণ্টা}$ চলে। প্রতি ইউনিট বিদ্যুতের মূল্য $7.50\text{ টাকা}$ হলে মে মাসে (৩১ দিন) বিদ্যুৎ বিল কত আসবে?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 23)।</t>
+          <t>দৈনিক শক্তি ব্যয়: ফ্যান $= 5 \times 60 \times 8 = 2400\text{ Wh} = 2.4\text{ kWh}$। বাতি $= 10 \times 40 \times 6 = 2400\text{ Wh} = 2.4\text{ kWh}$। এসি $= 1500 \times 4 = 6000\text{ Wh} = 6.0\text{ kWh}$। দৈনিক মোট $= 2.4 + 2.4 + 6.0 = 10.8\text{ kWh}$। মে মাসে (৩১ দিন) মোট ইউনিট $= 10.8 \times 31 = 334.8\text{ kWh}$। বিদ্যুৎ বিল $= 334.8 \times 7.50 = 2511.0\text{ টাকা}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>বিদ্যুৎ বিল $= 2511.0\text{ টাকা}$ (মোট শক্তি $334.8\text{ kWh}$)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4858,7 +4594,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী (সমস্যা 24)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4871,31 +4607,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-[সমস্যা 24: কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী]
-##PRESET:circuit-resistors[size:medium]##
-দুটি তড়িৎকোষ $E_1 = 2\text{ V}$ ($r_1 = 1\ \Omega$) এবং $E_2 = 15\text{ V}$ ($r_2 = 2\ \Omega$) একটি সাধারণ রোধ $R = 10\ \Omega$-এর সাথে সমান্তরালে যুক্ত। কার্শফের সূত্র প্রয়োগ করে রোধক $R$-এর মধ্য দিয়ে মূল প্রবাহ কত নির্ণয় কর।</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি নিমজ্জিত হিটার $220\text{ V}$ মেইন্সে যুক্ত অবস্থায় $5.0\text{ A}$ কারেন্ট টানে। হিটারটি $10\text{ মিনিটে}$ কত জুল তাপ উৎপন্ন করবে এবং কত ক্যালোরি তাপ উৎপন্ন হবে? ($1\text{ cal} = 4.184\text{ J}$)।</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 24)।</t>
+          <t>উৎপন্ন তাপ $H = V I t = 220\text{ V} \times 5.0\text{ A} \times (10 \times 60\text{ s}) = 1100 \times 600 = 660000\text{ J} = 6.60 \times 10^5\text{ J}$। ক্যালোরিতে $H = \frac{660000}{4.184} \approx 157743.8\text{ cal} \approx 1.577 \times 10^5\text{ cal}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>উৎপন্ন তাপ $H = 6.60 \times 10^5\text{ J} = 660.0\text{ kJ}$, ক্যালোরিতে $1.577 \times 10^5\text{ cal}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4915,38 +4645,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power) (সমস্যা 25)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power)]
-একটি ব্যাটারির তড়িৎচালক বল $E = 4\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 3\ \Omega$। ব্যাটারিটির সাথে একটি পরিবর্তনশীল বহিঃস্থ রোধ $R$ যুক্ত করা হলো। বহিঃস্থ রোধে সর্বোচ্চ ক্ষমতা পেতে $R$-এর মান কত হতে হবে এবং সর্বোচ্চ ক্ষমতার মান কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=3][size:small]##
+একটি ফিউজ তারের ব্যাস $d = 0.5\text{ mm}$ এবং এটি $5.0\text{ A}$ প্রবাহে গলে যায়। একই উপাদানের অন্য একটি ফিউজ তারের ব্যাস $1.0\text{ mm}$ হলে এটি কত প্রবাহে গলে যাবে? (পেয়ারের নীতি $I \propto d^{3/2}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 25)।</t>
+          <t>ফিউজ তারের প্রবাহ ধারণ ক্ষমতা $I \propto d^{3/2}$। $\frac{I_2}{I_1} = \left(\frac{d_2}{d_1}\right)^{3/2} = \left(\frac{1.0}{0.5}\right)^{3/2} = 2^{3/2} = 2\sqrt{2} \approx 2.8284$। নতুন গলন প্রবাহ $I_2 = 5.0 \times 2.8284 \approx 14.14\text{ A}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>গলন প্রবাহ $I_2 = 14.14\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4966,7 +4696,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা (সমস্যা 26)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4979,25 +4709,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা]
-একটি টাংস্টেন বাতির ফিলামেন্টের রোধ $0^\circ\text{C}$-এ $R_0 = 60\ \Omega$। বাতিটি জ্বালানোর পর রোধ বৃদ্ধি পেয়ে $R_t = 600\ \Omega$ হলো। টাংস্টেনের উষ্ণতা সহগ $\alpha = 4.5 \times 10^{-3}\text{ K}^{-1}$ হলে ফিলামেন্টের চূড়ান্ত তাপমাত্রা কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=2][size:small]##
+একটি হিটারের কুণ্ডলীকে কেটে সমান দুই টুকরা করে একটি টুকরা ব্যবহার করলে হিটারটির উৎপন্ন তাপের হার আদি হারের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 26)।</t>
+          <t>মেইন ভোল্টেজ $V$ স্থির থাকে। তাপ উৎপাদন হার $P = \frac{V^2}{R}$। কুণ্ডলী অর্ধেক কাটলে রোধ অর্ধেক হয়ে যায় ($R' = R/2$)। নতুন ক্ষমতা $P' = \frac{V^2}{R/2} = 2 \frac{V^2}{R} = 2P$। অতএব তাপ উৎপাদনের হার দ্বিগুণ হবে।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>উৎপন্ন তাপের হার দ্বিগুণ ($2.0$ গুণ) হবে</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5017,38 +4747,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি (সমস্যা 27)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি]
-একটি গ্যালভানোমিটারের রোধ $G = 800\ \Omega$ এবং এটি সর্বোচ্চ $I_g = 9\text{ mA}$ প্রবাহ নিরাপদে গ্রহণ করতে পারে। এর সাহায্যে $I = 10\text{ A}$ পর্যন্ত বিদ্যুৎ প্রবাহ পরিমাপের জন্য কত মানের শান্ট ($S = \frac{I_g G}{I - I_g}$) যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গ্যালভানোমিটারের রোধ $G = 50\text{ }\Omega$ এবং পূর্ণ স্কেল বিক্ষেপের প্রবাহ $I_g = 2\text{ mA}$। এর সাথে $S = 0.05\text{ }\Omega$ শান্ট যুক্ত করলে অ্যামিটারটির সামগ্রিক তুল্য রোধ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 27)।</t>
+          <t>অ্যামিটারের তুল্য রোধ $R_A = \frac{G S}{G + S} = \frac{50 \times 0.05}{50 + 0.05} = \frac{2.5}{50.05} \approx 0.04995\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>সামগ্রিক তুল্য রোধ $R_A = 0.04995\text{ }\Omega \approx 0.05\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5068,7 +4798,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ (সমস্যা 28)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5081,25 +4811,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ]
-একটি $G = 100\ \Omega$ রোধের গ্যালভানোমিটার দিয়ে পূর্ণ স্কেল বিক্ষেপের জন্য $I_g = 12\text{ mA}$ প্রয়োজন। এটিকে $0 - 100\text{ V}$ পাল্লার ভোল্টমিটারে রূপান্তর করতে কত মানের রোধ শ্রেণিতে যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ভোল্টমিটারের অভ্যন্তরীণ রোধ $R_v = 10000\text{ }\Omega$ এবং এটি $100\text{ V}$ পর্যন্ত মাপতে পারে। এর পাল্লা বাড়িয়ে $500\text{ V}$ করতে হলে এর সাথে কত মানের রোধ যুক্ত করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 28)।</t>
+          <t>গুণক সংখ্যা $n = \frac{V'}{V} = \frac{500}{100} = 5$। প্রয়োজনীয় শ্রেণি রোধ $R = (n - 1)R_v = (5 - 1) \times 10000 = 4 \times 10000 = 40000.0\text{ }\Omega = 40.0\text{ k}\Omega$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>শ্রেণিতে অতিরিক্ত রোধ $R = 40000.0\text{ }\Omega = 40.0\text{ k}\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5119,38 +4849,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায় (সমস্যা 29)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায়]
-প্রতিটি $E = 1.5\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 0.12\ \Omega$ বিশিষ্ট 15টি কোষকে শ্রেণিতে যুক্ত করে $R = 10\ \Omega$ বহিঃস্থ রোধের সাথে সংযোগ দিলে বর্তনীর মোট প্রবাহ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি $10\text{ V}$ ব্যাটারি এবং $1.0\text{ }\Omega$ অভ্যন্তরীণ রোধযুক্ত উৎস $R$ রোধের মধ্য দিয়ে প্রবাহ পাঠায়। রোধ $R$-এ ব্যয়িত ক্ষমতা সর্বোচ্চ হলে প্রতি সেকেন্ডে ব্যাটারির রাসায়নিক শক্তির কত অংশ তাপে রূপান্তরিত হয়?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 29)।</t>
+          <t>সর্বোচ্চ ক্ষমতা স্থানান্তরের সময় $R = r = 1.0\text{ }\Omega$। ফলে অভ্যন্তরীণ বিভব পতন এবং লোড বিভব পতন সমান ($V_{\text{load}} = E/2$)। ব্যাটারির মোট ক্ষমতা $P_{\text{total}} = E I = \frac{E^2}{2r}$ যার অর্ধেক ($50\%$) লোডে যায় এবং অর্ধেক ($50\%$) ব্যাটারির অভ্যন্তরীণ রোধে অপচয় হয়।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>উৎপন্ন মোট শক্তির ঠিক $50\%$ অংশ বহিস্থ রোধে এবং $50\%$ অংশ অভ্যন্তরীণ রোধে অপচয় হয় (দক্ষতা $50\%$)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5170,7 +4900,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব (সমস্যা 30)</t>
+          <t>জুলের তাপীয় ক্রিয়া, তড়িৎ ক্ষমতা ও মিটার রূপান্তর (Joule Heating &amp; Meters)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5183,25 +4913,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব]
-একটি বাসায় প্রতিদিন $2$টি $60\text{ W}$-এর বাতি ৫ ঘণ্টা এবং 3টি $80\text{ W}$-এর ফ্যান ১০ ঘণ্টা করে চলে। প্রতি ইউনিট বিদ্যুতের মূল্য ৮ টাকা হলে ৩০ দিনের এক মাসে বিদ্যুৎ বিল কত টাকা আসবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি অ্যামিটারের মূল প্রবাহের $1\%$ গ্যালভানোমিটারের মধ্য দিয়ে যায়। গ্যালভানোমিটারের রোধ $G = 99\text{ }\Omega$ হলে শান্টের রোধ $S$ কত?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 30)।</t>
+          <t>প্রশ্নমতে $I_g = 0.01 I \implies I = 100 I_g$। শান্টের সূত্র: $S = \frac{I_g G}{I - I_g} = \frac{I_g \times 99}{100 I_g - I_g} = \frac{99 I_g}{99 I_g} = 1.0\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>শান্ট রোধ $S = 1.0\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5221,44 +4951,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ (সমস্যা 31)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##
-[সমস্যা 31: হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ]
-##PRESET:circuit-wheatstone[size:medium]##
-একটি হুইটস্টোন ব্রিজের চার বাহুর রোধ যথাক্রমে $P = 4\ \Omega$, $Q = 6\ \Omega$, $R = 8\ \Omega$, এবং $S = 30\ \Omega$। ব্রিজটিকে সাম্যাবস্থায় আনতে চতুর্থ বাহুর সাথে কত মানের রোধ সমান্তরালে বা শ্রেণিতে যুক্ত করতে হবে?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি অসমান্তরাল প্রতিসম ব্রিজে $A$ ও $B$-এর মাঝে পাঁচটি রোধক যুক্ত: $R_1 = 2\text{ }\Omega, R_2 = 4\text{ }\Omega, R_3 = 4\text{ }\Omega, R_4 = 2\text{ }\Omega$ এবং কর্ণীয় গ্যালভানোমিটার শাখায় $R_5 = 5\text{ }\Omega$। ব্রিজটির দুই প্রান্তের তুল্য রোধ $R_{AB}$ ডেল্টা-স্টার রূপান্তর বা নোডাল বিশ্লেষণ দ্বারা নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 31)।</t>
+          <t>ডেল্টা-স্টার বা নোড সমীকরণ ব্যবহার করে: প্রতিসাম্যের কারণে প্রান্তিক বিভব সম্পর্ক থেকে তুল্য রোধ $R_{AB} = \frac{2 R_1 R_2 + R_5(R_1 + R_2)}{R_1 + R_2 + 2 R_5} = \frac{2(2)(4) + 5(2+4)}{2 + 4 + 2(5)} = \frac{16 + 30}{6 + 10} = \frac{46}{16} = 2.875\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>তুল্য রোধ $R_{AB} = 2.80\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5278,12 +5002,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ (সমস্যা 32)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5291,25 +5015,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ]
-একটি মিটার ব্রিজের বাম ফাঁকে $R = 6\ \Omega$ রোধ এবং ডান ফাঁকে একটি অজানা রোধ $S$ যুক্ত করলে বাম প্রান্ত হতে $l = 90\text{ cm}$ দূরত্বে নিরপেক্ষ বিন্দু পাওয়া যায়। অজানা রোধ $S$ এবং তারটির ব্যাসার্ধ $0.5\text{ mm}$ ও দৈর্ঘ্য $1\text{ m}$ হলে আপেক্ষিক রোধ কত?</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সুষম তারের তৈরি বৃত্তাকার বলয়ের ব্যাসার্ধ $r$ এবং সম্পূর্ণ পরিধির মোট রোধ $R = 12\text{ }\Omega$। বৃত্তের পরিধির ওপর $120^\circ$ ব্যবধানে অবস্থিত দুটি বিন্দু $A$ ও $B$-এর মধ্যবর্তী তুল্য রোধ কত?</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 32)।</t>
+          <t>$120^\circ$ চাপটির দৈর্ঘ্য সমগ্র পরিধির $1/3$ অংশ, ফলে এর রোধ $R_1 = \frac{12}{3} = 4.0\text{ }\Omega$। অবশিষ্ট $240^\circ$ চাপের রোধ $R_2 = 12 - 4 = 8.0\text{ }\Omega$। এই দুই অংশ পরস্পরের সাথে সমান্তরালে যুক্ত: $R_{AB} = \frac{R_1 R_2}{R_1 + R_2} = \frac{4 \times 8}{4 + 8} = \frac{32}{12} = \frac{8}{3}\text{ }\Omega \approx 2.667\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>তুল্য রোধ $R_{AB} = 2.67\text{ }\Omega = \frac{8}{3}\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5329,38 +5053,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা (সমস্যা 33)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা]
-একটি পোটেনশিওমিটার তারের দৈর্ঘ্য $10\text{ m}$ এবং রোধ $80\ \Omega$। এর সাথে শ্রেণি সমবায়ে একটি ব্যাটারি ও রোধক যুক্ত করায় প্রতি মিটারে বিভব পতন $0.012\text{ V/m}$। একটি প্রমাণ কোষের জন্য নিস্পন্দ দৈর্ঘ্য $l = 60\text{ cm}$ হলে কোষটির তড়িৎচালক বল কত?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি পটেনশিওমিটার তারের দৈর্ঘ্য $4.0\text{ m}$ এবং রোধ $8.0\text{ }\Omega$। তারটির সাথে $2.0\text{ V}$ ও নগণ্য অভ্যন্তরীণ রোধের একটি প্রমাণ কোষ এবং একটি পরিবর্তনশীল রোধক যুক্ত আছে। তারের প্রতি মিটারে $1.0\text{ mV}$ বিভব পতন সৃষ্টি করতে হলে পরিবর্তনশীল রোধকের মান কত ওহম করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 33)।</t>
+          <t>তারের মোট দৈর্ঘ্য $4.0\text{ m}$। প্রতি মিটারে $1.0\text{ mV} = 10^{-3}\text{ V}$ পতন হলে তারের মোট বিভব পতন $V_w = 4.0 \times 10^{-3}\text{ V}$। প্রয়োজনীয় প্রবাহ $I = \frac{V_w}{R_w} = \frac{4.0 \times 10^{-3}}{8.0} = 5.0 \times 10^{-4}\text{ A}$। মোট রোধ $R_{\text{total}} = \frac{E}{I} = \frac{2.0}{5.0 \times 10^{-4}} = 4000.0\text{ }\Omega$। পরিবর্তনশীল রোধক $R_s = R_{\text{total}} - R_w = 4000 - 8 = 3992.0\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>পরিবর্তনশীল রোধক $R_s = 3992.0\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5380,12 +5104,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী (সমস্যা 34)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5393,31 +5117,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-[সমস্যা 34: কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী]
-##PRESET:circuit-resistors[size:medium]##
-দুটি তড়িৎকোষ $E_1 = 10\text{ V}$ ($r_1 = 1\ \Omega$) এবং $E_2 = 15\text{ V}$ ($r_2 = 2\ \Omega$) একটি সাধারণ রোধ $R = 10\ \Omega$-এর সাথে সমান্তরালে যুক্ত। কার্শফের সূত্র প্রয়োগ করে রোধক $R$-এর মধ্য দিয়ে মূল প্রবাহ কত নির্ণয় কর।</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি মিটার ব্রিজের বাম ফাঁকের রোধ $2.0\text{ }\Omega$ এবং ডান ফাঁকের রোধ $3.0\text{ }\Omega$ হলে নিস্পন্দ বিন্দু পাওয়া যায় $l_1 = 40.5\text{ cm}$ পাঠে। প্রান্তিক রোধের ত্রুটি (End error) বিবেচনা করে বাম ও ডান প্রান্তের প্রান্তীয় সংশোধন যথাক্রমে $lpha$ ও $eta$ নির্ণয়ের সমীকরণ গঠন কর।</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 34)।</t>
+          <t>প্রান্তিক সংশোধন বিবেচনায় মিটার ব্রিজ সমীকরণ: $\frac{R_1}{R_2} = \frac{l + \alpha}{(100 - l) + \beta}$। দুটি ভিন্ন জানা রোধের সেট ব্যবহার করে দুটি যুগপৎ সমীকরণ গঠনের মাধ্যমে প্রান্তিক রোধের ত্রুটি $\alpha$ ও $\beta$ নিখুঁতভাবে অপনয়ন করা হয়।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>বাম প্রান্ত সংশোধন $\alpha = 0.5\text{ cm}$, ডান প্রান্ত সংশোধন $\beta = 1.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5437,38 +5155,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power) (সমস্যা 35)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power)]
-একটি ব্যাটারির তড়িৎচালক বল $E = 12\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 3\ \Omega$। ব্যাটারিটির সাথে একটি পরিবর্তনশীল বহিঃস্থ রোধ $R$ যুক্ত করা হলো। বহিঃস্থ রোধে সর্বোচ্চ ক্ষমতা পেতে $R$-এর মান কত হতে হবে এবং সর্বোচ্চ ক্ষমতার মান কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি তামা ও একটি লোহার তারের দৈর্ঘ্য ও প্রস্থচ্ছেদ সমান। তার দুটিকে শ্রেণিতে যুক্ত করে নির্দিষ্ট বিভব পার্থক্য প্রয়োগ করলে কোন তারটিতে বেশি তাপ উৎপন্ন হবে? (লোহার আপেক্ষিক রোধ তামার চেয়ে প্রায় ৬ গুণ বেশি)।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 35)।</t>
+          <t>শ্রেণি সমবায়ে উভয় তারে প্রবাহ $I$ সমান। উৎপন্ন তাপ $H = I^2 R t \propto R \propto \rho$। যেহেতু লোহার আপেক্ষিক রোধ তামার চেয়ে ৬ গুণ বেশি ($\rho_{\text{Fe}} \approx 6\rho_{\text{Cu}}$), তাই লোহার তারের রোধ বেশি এবং এতে ৬ গুণ বেশি তাপ শক্তি নির্গত হবে।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>লোহার তারে প্রায় ৬ গুণ বেশি তাপ উৎপন্ন হবে</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5488,12 +5206,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা (সমস্যা 36)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5501,25 +5219,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা]
-একটি টাংস্টেন বাতির ফিলামেন্টের রোধ $0^\circ\text{C}$-এ $R_0 = 20\ \Omega$। বাতিটি জ্বালানোর পর রোধ বৃদ্ধি পেয়ে $R_t = 600\ \Omega$ হলো। টাংস্টেনের উষ্ণতা সহগ $\alpha = 4.5 \times 10^{-3}\text{ K}^{-1}$ হলে ফিলামেন্টের চূড়ান্ত তাপমাত্রা কত?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+উপরের সমস্যায় তার দুটিকে সমান্তরাল সমবায়ে যুক্ত করলে কোন তারটিতে বেশি তাপ উৎপন্ন হবে?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 36)।</t>
+          <t>সমান্তরাল সমবায়ে বিভব পার্থক্য $V$ সমান থাকে। উৎপন্ন তাপের হার $P = \frac{V^2}{R} \propto \frac{1}{R} \propto \frac{1}{\rho}$। তামার রোধ কম হওয়ায় তামার তারের মধ্য দিয়ে বেশি তড়িৎ প্রবাহিত হবে এবং এতে ৬ গুণ বেশি তাপ উৎপন্ন হবে।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>তামার তারে প্রায় ৬ গুণ বেশি তাপ উৎপন্ন হবে</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5539,38 +5257,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি (সমস্যা 37)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি]
-একটি গ্যালভানোমিটারের রোধ $G = 400\ \Omega$ এবং এটি সর্বোচ্চ $I_g = 9\text{ mA}$ প্রবাহ নিরাপদে গ্রহণ করতে পারে। এর সাহায্যে $I = 10\text{ A}$ পর্যন্ত বিদ্যুৎ প্রবাহ পরিমাপের জন্য কত মানের শান্ট ($S = \frac{I_g G}{I - I_g}$) যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ব্যাটারির তড়িচ্চালক বল $E = 6.0\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 1.0\text{ }\Omega$। ব্যাটারিটির সাথে একটি $5.0\text{ }\Omega$ বহিস্থ রোধ যুক্ত থাকলে ব্যাটারির টার্মিনাল ভোল্টেজ কত হবে? যদি ব্যাটারিটির দুই প্রান্ত শর্ট সার্কিট করা হয়, তবে শর্ট সার্কিট প্রবাহ কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 37)।</t>
+          <t>প্রবাহ $I = \frac{E}{R + r} = \frac{6.0}{5.0 + 1.0} = 1.0\text{ A}$। টার্মিনাল ভোল্টেজ $V = E - I r = 6.0 - (1.0)(1.0) = 5.0\text{ V}$ (বা $V = I R = 1.0 \times 5.0 = 5.0\text{ V}$)। শর্ট সার্কিট অবস্থায় $R = 0 \implies I_{\text{sc}} = \frac{E}{r} = \frac{6.0}{1.0} = 6.0\text{ A}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>টার্মিনাল ভোল্টেজ $V = 5.0\text{ V}$, শর্ট সার্কিট কারেন্ট $I_{\text{sc}} = 6.0\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5590,12 +5308,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ (সমস্যা 38)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5603,25 +5321,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ]
-একটি $G = 60\ \Omega$ রোধের গ্যালভানোমিটার দিয়ে পূর্ণ স্কেল বিক্ষেপের জন্য $I_g = 12\text{ mA}$ প্রয়োজন। এটিকে $0 - 100\text{ V}$ পাল্লার ভোল্টমিটারে রূপান্তর করতে কত মানের রোধ শ্রেণিতে যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+তিনটি সমান রোধক $R$ দ্বারা একটি 'T' বা 'Y' নেটওয়ার্ক গঠিত। সমতুল্য 'ডেল্টা' ($\Delta$) নেটওয়ার্কের প্রতিটি বাহুর রোধ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 38)।</t>
+          <t>স্টার হতে ডেল্টা রূপান্তর সূত্র: $R_{ab} = R_a + R_b + \frac{R_a R_b}{R_c}$। তিনটি বাহু সমান ($R_a = R_b = R_c = R$) হলে: $R_{ab} = R + R + \frac{R^2}{R} = 2R + R = 3R$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>প্রতিটি বাহুর রোধ $R_\Delta = 3 R$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5641,38 +5359,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায় (সমস্যা 39)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায়]
-প্রতিটি $E = 1.5\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 0.8\ \Omega$ বিশিষ্ট 15টি কোষকে শ্রেণিতে যুক্ত করে $R = 10\ \Omega$ বহিঃস্থ রোধের সাথে সংযোগ দিলে বর্তনীর মোট প্রবাহ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বর্তনীতে $220\text{ V}$ উৎসের সাথে $100\text{ W}$ বাতি যুক্ত। বাতির ফিলামেন্টের রোধ গরম অবস্থায় ঠান্ডা অবস্থার চেয়ে ১০ গুণ বেশি। বাতিটি জ্বালানোর ঠিক শুরুর মুহূর্তে প্রারম্ভিক ইনরাশ কারেন্ট (Inrush current) কত অ্যাম্পিয়ার?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 39)।</t>
+          <t>স্বাভাবিক অবস্থায় রোধ $R_{\text{hot}} = \frac{V^2}{P} = \frac{220^2}{100} = 484\text{ }\Omega$। স্বাভাবিক প্রবাহ $I_{\text{normal}} = \frac{100}{220} \approx 0.4545\text{ A}$। ঠান্ডা অবস্থায় রোধ $R_{\text{cold}} = \frac{R_{\text{hot}}}{10} = 48.4\text{ }\Omega$। সুইচ অন করার মুহূর্তে প্রবাহ $I_0 = \frac{V}{R_{\text{cold}}} = \frac{220}{48.4} \approx 4.545\text{ A}$ (স্বাভাবিকের ১০ গুণ বেশি, যে কারণে বাতি সাধারণত সুইচ অন করার মুহূর্তেই কাটে)।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>প্রারম্ভিক ইনরাশ কারেন্ট $I_0 = 4.545\text{ A}$ (স্বাভাবিক কারেন্ট $0.455\text{ A}$)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5692,12 +5410,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব (সমস্যা 40)</t>
+          <t>উন্নত নেটওয়ার্ক, পটেনশিওমিটার ও ব্রিজ বর্তনী (Advanced Networks &amp; Bridges)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5705,25 +5423,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব]
-একটি বাসায় প্রতিদিন $10$টি $60\text{ W}$-এর বাতি ৫ ঘণ্টা এবং 3টি $80\text{ W}$-এর ফ্যান ১০ ঘণ্টা করে চলে। প্রতি ইউনিট বিদ্যুতের মূল্য ৮ টাকা হলে ৩০ দিনের এক মাসে বিদ্যুৎ বিল কত টাকা আসবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি অ্যামিটারের রোধ $0.8\text{ }\Omega$ এবং এটি $1.0\text{ A}$ পর্যন্ত পরিমাপ করতে পারে। অ্যামিটারটির সাথে $0.2\text{ }\Omega$ শান্ট যুক্ত করা হলে নতুন অবস্থায় এটি কত অ্যাম্পিয়ার পর্যন্ত পরিমাপ করতে পারবে?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 40)।</t>
+          <t>শান্টের সমীকরণ: $S = \frac{I_A R_A}{I - I_A} \implies 0.2 = \frac{1.0 \times 0.8}{I - 1.0} \implies 0.2(I - 1.0) = 0.8 \implies I - 1.0 = \frac{0.8}{0.2} = 4.0 \implies I = 5.0\text{ A}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>সর্বোচ্চ পরিমাপ্য প্রবাহ $I = 5.0\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5743,44 +5461,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ (সমস্যা 41)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##
-[সমস্যা 41: হুইটস্টোন ব্রিজের সাম্যাবস্থা ও চতুর্থ বাহুর রোধ]
-##PRESET:circuit-wheatstone[size:medium]##
-একটি হুইটস্টোন ব্রিজের চার বাহুর রোধ যথাক্রমে $P = 12\ \Omega$, $Q = 6\ \Omega$, $R = 8\ \Omega$, এবং $S = 30\ \Omega$। ব্রিজটিকে সাম্যাবস্থায় আনতে চতুর্থ বাহুর সাথে কত মানের রোধ সমান্তরালে বা শ্রেণিতে যুক্ত করতে হবে?</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি অসীম রোধক ল্যাডার নেটওয়ার্কে প্রতিটি অনুভূমিক রোধ $R_1 = 1.0\text{ }\Omega$ এবং প্রতিটি উল্লম্ব রোধ $R_2 = 2.0\text{ }\Omega$। ইনপুট প্রান্তদ্বয়ের মধ্যবর্তী তুল্য রোধ $R_{\text{in}}$ কত ওহম?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-wheatstone[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 41)।</t>
+          <t>অসীম ল্যাডারের তুল্য রোধ $X$ হলে: $X = R_1 + \frac{R_2 X}{R_2 + X} = 1.0 + \frac{2X}{2 + X}$। সমীকরণ সমাধান: $X(2 + X) = (2 + X) + 2X \implies 2X + X^2 = 2 + 3X \implies X^2 - X - 2 = 0 \implies (X - 2)(X + 1) = 0$। রোধ ধনাত্মক হওয়ায় $X = 2.0\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>তুল্য রোধ $R_{\text{in}} = 2.0\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5800,12 +5512,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ (সমস্যা 42)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5813,25 +5525,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: মিটার ব্রিজ ও অজানা তারের আপেক্ষিক রোধ]
-একটি মিটার ব্রিজের বাম ফাঁকে $R = 2\ \Omega$ রোধ এবং ডান ফাঁকে একটি অজানা রোধ $S$ যুক্ত করলে বাম প্রান্ত হতে $l = 90\text{ cm}$ দূরত্বে নিরপেক্ষ বিন্দু পাওয়া যায়। অজানা রোধ $S$ এবং তারটির ব্যাসার্ধ $0.5\text{ mm}$ ও দৈর্ঘ্য $1\text{ m}$ হলে আপেক্ষিক রোধ কত?</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ব্যাটারি যার $E = 10\text{ V}$ এবং $r = 1\text{ }\Omega$, অপর একটি ব্যাটারি $E = 15\text{ V}$ ও $r = 2\text{ }\Omega$-এর সাথে বিপরীত সমান্তরালে (Back-to-back parallel) যুক্ত। সাধারণ টার্মিনালের খোলা বর্তনী ভোল্টেজ এবং সমতুল্য অভ্যন্তরীণ রোধ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 42)।</t>
+          <t>মিলম্যানের উপপাদ্য অনুসারে: $E_{\text{eq}} = \frac{E_1/r_1 + E_2/r_2}{1/r_1 + 1/r_2} = \frac{10/1 + 15/2}{1/1 + 1/2} = \frac{10 + 7.5}{1 + 0.5} = \frac{17.5}{1.5} \approx 11.667\text{ V}$। সমতুল্য অভ্যন্তরীণ রোধ $r_{\text{eq}} = \frac{r_1 r_2}{r_1 + r_2} = \frac{1 \times 2}{1 + 2} = \frac{2}{3} \approx 0.667\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>খোলা বর্তনী ভোল্টেজ $V = 11.67\text{ V}$, সমতুল্য অভ্যন্তরীণ রোধ $r_{\text{eq}} = 0.667\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5851,38 +5563,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা (সমস্যা 43)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: পোটেনশিওমিটার তারে তড়িৎচালক বল তুলনা]
-একটি পোটেনশিওমিটার তারের দৈর্ঘ্য $10\text{ m}$ এবং রোধ $40\ \Omega$। এর সাথে শ্রেণি সমবায়ে একটি ব্যাটারি ও রোধক যুক্ত করায় প্রতি মিটারে বিভব পতন $0.012\text{ V/m}$। একটি প্রমাণ কোষের জন্য নিস্পন্দ দৈর্ঘ্য $l = 100\text{ cm}$ হলে কোষটির তড়িৎচালক বল কত?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=3][size:small]##
+একটি সুষম তামার তারের রোধ $R$। তারটিকে কেটে সমান $n$টি টুকরা করে টুকরাগুলোকে সমান্তরালে যুক্ত করা হলো। নতুন সমবায়ের তুল্য রোধ আদি রোধের কত অংশ হবে?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 43)।</t>
+          <t>প্রতিটি টুকরার রোধ $r = \frac{R}{n}$। এরূপ $n$টি টুকরা সমান্তরালে যুক্ত করলে সমবায়ের তুল্য রোধ $R' = \frac{r}{n} = \frac{R/n}{n} = \frac{R}{n^2}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>নতুন তুল্য রোধ $R' = \frac{R}{n^2}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5902,12 +5614,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী (সমস্যা 44)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5915,31 +5627,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-[সমস্যা 44: কার্শফের সূত্রে বহু-লুপ জটিল বর্তনী]
-##PRESET:circuit-resistors[size:medium]##
-দুটি তড়িৎকোষ $E_1 = 6\text{ V}$ ($r_1 = 1\ \Omega$) এবং $E_2 = 15\text{ V}$ ($r_2 = 2\ \Omega$) একটি সাধারণ রোধ $R = 10\ \Omega$-এর সাথে সমান্তরালে যুক্ত। কার্শফের সূত্র প্রয়োগ করে রোধক $R$-এর মধ্য দিয়ে মূল প্রবাহ কত নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গ্যালভানোমিটারের পূর্ণ স্কেল বিক্ষেপের জন্য ভোল্টেজ প্রয়োজন $V_g = 50\text{ mV}$। এটিকে $5.0\text{ A}$ পূর্ণ স্কেলের একটি অ্যামিটারে রূপান্তর করতে প্রয়োজনীয় শান্টের রোধ কত?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 44)।</t>
+          <t>গ্যালভানোমিটারের দুই প্রান্তে সর্বোচ্চ ভোল্টেজ $V_g = 50\text{ mV} = 0.050\text{ V}$। শান্ট সমান্তরালে থাকায় শান্টের ভোল্টেজও $0.050\text{ V}$ হবে। যেহেতু $I_g \ll I$, তাই শান্টের মধ্য দিয়ে প্রায় সমস্ত কারেন্ট ($5.0\text{ A}$) প্রবাহিত হয়: $S \approx \frac{V_g}{I} = \frac{0.050\text{ V}}{5.0\text{ A}} = 0.010\text{ }\Omega = 10.0\text{ m}\Omega$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>প্রয়োজনীয় শান্ট $S = 0.010\text{ }\Omega = 10.0\text{ m}\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5959,38 +5665,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power) (সমস্যা 45)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: সর্বোচ্চ ক্ষমতা সঞ্চালন উপপাদ্য (Max Power)]
-একটি ব্যাটারির তড়িৎচালক বল $E = 8\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 3\ \Omega$। ব্যাটারিটির সাথে একটি পরিবর্তনশীল বহিঃস্থ রোধ $R$ যুক্ত করা হলো। বহিঃস্থ রোধে সর্বোচ্চ ক্ষমতা পেতে $R$-এর মান কত হতে হবে এবং সর্বোচ্চ ক্ষমতার মান কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি বৈদ্যুতিক কেটলিতে দুটি হিটিং কয়েল রয়েছে। ১ম কয়েলটি একা ব্যবহার করলে পানি ফুটতে $10\text{ মিনিট}$ এবং ২য় কয়েলটি একা ব্যবহার করলে $15\text{ মিনিট}$ সময় লাগে। কয়েল দুটিকে (ক) শ্রেণিতে এবং (খ) সমান্তরালে ব্যবহার করলে একই পরিমাণ পানি ফুটতে কত মিনিট সময় লাগবে?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 45)।</t>
+          <t>প্রয়োজনীয় তাপ $H$ স্থির। ক্ষমতা $P \propto 1/t \implies R \propto t$। (ক) শ্রেণিতে রোধ যোগ হয়: $R_s = R_1 + R_2 \implies t_s = t_1 + t_2 = 10 + 15 = 25.0\text{ মিনিট}$। (খ) সমান্তরালে ক্ষমতা যোগ হয়: $P_p = P_1 + P_2 \implies \frac{1}{t_p} = \frac{1}{t_1} + \frac{1}{t_2} = \frac{1}{10} + \frac{1}{15} = \frac{3+2}{30} = \frac{5}{30} = \frac{1}{6} \implies t_p = 6.0\text{ মিনিট}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(ক) শ্রেণিতে $t_s = 25.0\text{ মিনিট}$, (খ) সমান্তরালে $t_p = 6.0\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6010,12 +5716,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা (সমস্যা 46)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6023,25 +5729,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: রোধের উষ্ণতা সহগ ও ফিলামেন্টের তাপমাত্রা]
-একটি টাংস্টেন বাতির ফিলামেন্টের রোধ $0^\circ\text{C}$-এ $R_0 = 100\ \Omega$। বাতিটি জ্বালানোর পর রোধ বৃদ্ধি পেয়ে $R_t = 600\ \Omega$ হলো। টাংস্টেনের উষ্ণতা সহগ $\alpha = 4.5 \times 10^{-3}\text{ K}^{-1}$ হলে ফিলামেন্টের চূড়ান্ত তাপমাত্রা কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি চল তড়িৎ বর্তনীতে ধারক ও রোধকের শ্রেণি সংযোগ (RC circuit): $C = 10\text{ }\mu	ext{F}$ এবং $R = 100\text{ k}\Omega$। বর্তনীটির সময় ধ্রুবক (Time constant $\tau$) কত? সুইচ অন করার কত সময় পর ধারকের আধান তার সর্বোচ্চ মানের $63.2\%$ অর্জন করবে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 46)।</t>
+          <t>$RC$ বর্তনীর সময় ধ্রুবক $\tau = R C = (100 \times 10^3\text{ }\Omega) \times (10 \times 10^{-6}\text{ F}) = 1.0\text{ s}$। চার্জিং সমীকরণ: $q(t) = Q_0(1 - e^{-t/\tau})$। $t = \tau$-তে $q = Q_0(1 - e^{-1}) = Q_0(1 - 0.368) = 0.632 Q_0$ ($63.2\%$ চার্জ অর্জিত হয়)। অতএব সময় $t = 1.0\text{ s}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>সময় ধ্রুবক $\tau = 1.0\text{ s}$, প্রয়োজনীয় সময় $t = 1.0\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6061,38 +5767,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি (সমস্যা 47)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: শান্ট ও গ্যালভানোমিটারের পাল্লা বৃদ্ধি]
-একটি গ্যালভানোমিটারের রোধ $G = 1200\ \Omega$ এবং এটি সর্বোচ্চ $I_g = 9\text{ mA}$ প্রবাহ নিরাপদে গ্রহণ করতে পারে। এর সাহায্যে $I = 10\text{ A}$ পর্যন্ত বিদ্যুৎ প্রবাহ পরিমাপের জন্য কত মানের শান্ট ($S = \frac{I_g G}{I - I_g}$) যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+ডিসচার্জিং প্রক্রিয়ায় একটি ধারকের ভোল্টেজ কত সময় পর তার প্রারম্ভিক মানের অর্ধেকে নেমে আসবে? (অর্ধায়ু $t_{1/2}$ ও সময় ধ্রুবক $\tau$-এর সম্পর্ক নির্ণয় কর)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 47)।</t>
+          <t>ডিসচার্জিং সমীকরণ: $V(t) = V_0 e^{-t/\tau}$। $V = V_0/2 \implies e^{-t/\tau} = 1/2 \implies e^{t/\tau} = 2 \implies t = \tau \ln(2) \approx 0.693 \tau$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>সময় $t_{1/2} = \tau \ln(2) \approx 0.693 \tau$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6112,12 +5818,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ (সমস্যা 48)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6125,25 +5831,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: ভোল্টমিটারে রূপান্তর ও শ্রেণি গুণক রোধ]
-একটি $G = 20\ \Omega$ রোধের গ্যালভানোমিটার দিয়ে পূর্ণ স্কেল বিক্ষেপের জন্য $I_g = 12\text{ mA}$ প্রয়োজন। এটিকে $0 - 100\text{ V}$ পাল্লার ভোল্টমিটারে রূপান্তর করতে কত মানের রোধ শ্রেণিতে যুক্ত করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গ্যালভানোমিটারের সাথে একটি শান্ট যুক্ত করায় এর সংবেদনশীলতা (Sensitivity) আদি মানের $1/n$ অংশ হয়ে যায়। গ্যালভানোমিটারের রোধ $G$ হলে শান্টের রোধ $S$ কত?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 48)।</t>
+          <t>সংবেদনশীলতা $1/n$ অংশ হওয়ার অর্থ হলো মোট প্রবাহের $1/n$ অংশ গ্যালভানোমিটার দিয়ে যায়: $I_g = \frac{I}{n}$। শান্ট সমীকরণ: $S = \frac{I_g G}{I - I_g} = \frac{(I/n)G}{I - I/n} = \frac{G/n}{(n-1)/n} = \frac{G}{n - 1}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$S = \frac{G}{n - 1}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6163,38 +5869,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায় (সমস্যা 49)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: কোষের শ্রেণি ও সমান্তরাল মিশ্র সমবায়]
-প্রতিটি $E = 1.5\text{ V}$ এবং অভ্যন্তরীণ রোধ $r = 0.4\ \Omega$ বিশিষ্ট 15টি কোষকে শ্রেণিতে যুক্ত করে $R = 10\ \Omega$ বহিঃস্থ রোধের সাথে সংযোগ দিলে বর্তনীর মোট প্রবাহ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##
+একটি বিদ্যুৎ বিতরণ লাইনের রোধ $R = 2.0\text{ }\Omega$। এই লাইনের মাধ্যমে $100\text{ kW}$ ক্ষমতা (ক) $250\text{ V}$ বিভবে এবং (খ) $10000\text{ V}$ উচ্চ বিভবে প্রেরণ করা হলে উভয় ক্ষেত্রে লাইনে অপচয়কৃত ক্ষমতার মান ও অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 49)।</t>
+          <t>প্রেরিত ক্ষমতা $P = V I \implies I = P/V$। লাইনে অপচয় $P_{\text{loss}} = I^2 R = \frac{P^2 R}{V^2}$। (ক) $V = 250\text{ V}$-এ $I = \frac{100000}{250} = 400\text{ A}$। অপচয় $P_{\text{loss}} = 400^2 \times 2 = 320000\text{ W} = 320\text{ kW}$ (উৎপন্ন ক্ষমতার চেয়েও বেশি অপচয়!)। (খ) $V = 10000\text{ V}$-এ $I = \frac{100000}{10000} = 10\text{ A}$। অপচয় $P_{\text{loss}} = 10^2 \times 2 = 200\text{ W} = 0.20\text{ kW}$ (মাত্র $0.2\%$ অপচয়)। এ কারণেই দূরপাল্লায় উচ্চ ভোল্টেজে বিদ্যুৎ প্রেরণ করা হয়।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(ক) নিম্ন ভোল্টেজে অপচয় $320.0\text{ kW}$ (অসম্ভব), (খ) উচ্চ ভোল্টেজে অপচয় মাত্র $200.0\text{ W} = 0.20\text{ kW}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6214,12 +5920,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব (সমস্যা 50)</t>
+          <t>উন্নত চল তড়িৎ ও অ-সরলরৈখিক বর্তনী (Advanced Current Electricity Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6227,25 +5933,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: বৈদ্যুতিক শক্তি ব্যয় ও বিদ্যুৎ বিল হিসাব]
-একটি বাসায় প্রতিদিন $6$টি $60\text{ W}$-এর বাতি ৫ ঘণ্টা এবং 3টি $80\text{ W}$-এর ফ্যান ১০ ঘণ্টা করে চলে। প্রতি ইউনিট বিদ্যুতের মূল্য ৮ টাকা হলে ৩০ দিনের এক মাসে বিদ্যুৎ বিল কত টাকা আসবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কার্শফের ভোল্টেজ সূত্র (KVL) এবং কার্শফের কারেন্ট সূত্র (KCL) যথাক্রমে কোন দুটি মৌলিক সংরক্ষণশীলতার নীতি (Conservation laws)-এর ওপর প্রতিষ্ঠিত?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ওহমের সূত্র, কার্শফের নিয়মাবলি ও হুইটস্টোন ব্রিজের সাম্যাবস্থা ব্যবহার করে গাণিতিক সমাধান (সমস্যা 50)।</t>
+          <t>কোনো সংযোগ বিন্দুতে (Junction) কোনো আধান জমা বা সৃষ্টি হতে পারে না; মোট অন্তর্মুখী আধান বহির্মুখী আধানের সমান—এটি আধানের সংরক্ষণশীলতা নির্দেশ করে (KCL)। আবার কোনো আবদ্ধ লুপে সম্পূর্ণ আবর্তনের পর তড়িৎ বিভবের মোট পরিবর্তন শূন্য হয় ($\oint \vec{E}\cdot d\vec{l} = 0$), অর্থাৎ স্থির তড়িৎ ক্ষেত্রে সম্পাদিত মোট কাজ শূন্য—এটি শক্তির সংরক্ষণশীলতার প্রত্যক্ষ রূপ (KVL)।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>চল তড়িতের সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>KCL আধানের সংরক্ষণশীলতা নীতি এবং KVL শক্তির সংরক্ষণশীলতা নীতির ওপর প্রতিষ্ঠিত</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
